--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A993A74-F124-4A91-A295-F4AFB8CA32EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1570828-ABCE-4571-BB37-17E946E6D6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -135,6 +135,10 @@
   </si>
   <si>
     <t>LIST&lt;INT&gt;_C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C_S</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -231,6 +235,107 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04AD00CC-1BCF-7EF1-71F1-A7FCDDC44474}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3981450" y="2228850"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AEE0DB9-922A-6338-BCEF-BABF61C34934}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3981450" y="2571750"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -521,7 +626,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -553,10 +658,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -571,7 +676,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>4</v>
@@ -751,9 +856,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="E14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="E16"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1570828-ABCE-4571-BB37-17E946E6D6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8392C1-D48D-4358-A3F6-0CA1B79AD4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -75,13 +75,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>puzzle_mechanism_id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>brush_area_id</t>
-  </si>
-  <si>
     <t>地编配置id</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -94,14 +87,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>谜题机关id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刷怪区域id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>add_kungfu</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -140,13 +125,51 @@
   <si>
     <t>INT_C_S</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>守卫1（火把）</t>
+  </si>
+  <si>
+    <t>火把</t>
+  </si>
+  <si>
+    <t>藤蔓吊桥</t>
+  </si>
+  <si>
+    <t>刷怪区域1</t>
+  </si>
+  <si>
+    <t>守卫2（过关点）</t>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备份</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>守卫1（蓝钥匙）</t>
+  </si>
+  <si>
+    <t>蓝门</t>
+  </si>
+  <si>
+    <t>守卫2（浮桥机关）</t>
+  </si>
+  <si>
+    <t>浮桥机关</t>
+  </si>
+  <si>
+    <t>小芽</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +197,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -189,7 +228,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -197,11 +236,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -218,6 +272,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -243,13 +303,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -291,13 +351,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -626,7 +686,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -635,14 +695,13 @@
     <col min="4" max="4" width="11.625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="3"/>
     <col min="6" max="6" width="21.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="58.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -651,17 +710,16 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -670,22 +728,19 @@
         <v>4</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -702,22 +757,19 @@
         <v>9</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -725,142 +777,262 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
-        <v>11001</v>
+        <v>10001</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="3">
-        <v>1001</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D5" s="8">
         <v>90000101</v>
       </c>
+      <c r="F5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
       <c r="H5" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" s="3">
-        <v>5</v>
-      </c>
-      <c r="J5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
-        <v>11002</v>
+        <v>10002</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
-      <c r="C6" s="3">
-        <v>1002</v>
-      </c>
-      <c r="E6" s="3">
-        <v>10011</v>
-      </c>
+      <c r="C6" s="8">
+        <v>44001</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="8"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
-        <v>11003</v>
+        <v>10003</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="3">
-        <v>1003</v>
-      </c>
-      <c r="D7" s="3">
-        <v>90000102</v>
-      </c>
+      <c r="C7" s="8">
+        <v>43001</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="8"/>
       <c r="H7" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I7" s="3">
-        <v>8</v>
-      </c>
-      <c r="J7" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
-        <v>11004</v>
+        <v>10004</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="3">
-        <v>1004</v>
-      </c>
-      <c r="G8" s="3">
-        <v>10001</v>
-      </c>
-      <c r="H8" s="3">
-        <v>20</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="C8" s="8">
+        <v>2001</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="F8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="8">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
-        <v>11005</v>
+        <v>10005</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
-        <v>1005</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="C9" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D9" s="9">
+        <v>90000102</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>10</v>
+      </c>
       <c r="I9" s="3">
-        <v>10</v>
-      </c>
-      <c r="J9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="E14"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="E16"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A10" s="4">
+        <v>20001</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D10" s="8">
+        <v>90000201</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A11" s="4">
+        <v>20002</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="8">
+        <v>16001</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A12" s="4">
+        <v>20003</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2001</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A13" s="4">
+        <v>20004</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D13" s="8">
+        <v>90000202</v>
+      </c>
+      <c r="E13"/>
+      <c r="F13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A14" s="4">
+        <v>20005</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+      <c r="C14" s="8">
+        <v>6001</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A15" s="4">
+        <v>20006</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="8">
+        <v>17001</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8392C1-D48D-4358-A3F6-0CA1B79AD4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37527F98-E580-41C8-8CA2-7A830FC8ED65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -111,10 +111,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>10,20,30,20,60,20,100,20,100,20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>STRING</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -163,6 +159,19 @@
   </si>
   <si>
     <t>小芽</t>
+  </si>
+  <si>
+    <t>守卫1（木头）</t>
+  </si>
+  <si>
+    <t>断桥</t>
+  </si>
+  <si>
+    <t>守卫2（蓝钥匙）</t>
+  </si>
+  <si>
+    <t>10,4,40,8,100,12,200,16,300,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -686,7 +695,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -716,10 +725,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -728,16 +737,16 @@
         <v>4</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -757,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -786,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -812,7 +821,7 @@
         <v>90000101</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
@@ -836,10 +845,12 @@
       </c>
       <c r="D6" s="8"/>
       <c r="F6" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="8"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>5</v>
+      </c>
       <c r="I6" s="3">
         <v>0</v>
       </c>
@@ -856,7 +867,7 @@
       </c>
       <c r="D7" s="8"/>
       <c r="F7" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="3">
@@ -878,14 +889,14 @@
       </c>
       <c r="D8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="8">
         <v>2</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -902,7 +913,7 @@
         <v>90000102</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
@@ -928,7 +939,7 @@
         <v>90000201</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="8">
         <v>1</v>
@@ -948,7 +959,7 @@
         <v>16001</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="8"/>
       <c r="I11" s="2">
@@ -966,7 +977,7 @@
         <v>2001</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="8">
         <v>2</v>
@@ -990,7 +1001,7 @@
       </c>
       <c r="E13"/>
       <c r="F13" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -1010,7 +1021,7 @@
         <v>6001</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="8"/>
       <c r="I14" s="2">
@@ -1028,9 +1039,119 @@
         <v>17001</v>
       </c>
       <c r="F15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A16" s="4">
+        <v>30001</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D16" s="8">
+        <v>90000301</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="2">
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" s="4">
+        <v>30002</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="8">
+        <v>28001</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="F17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A18" s="4">
+        <v>30003</v>
+      </c>
+      <c r="B18" s="3">
+        <v>3</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2001</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="F18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A19" s="4">
+        <v>30004</v>
+      </c>
+      <c r="B19" s="3">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D19" s="8">
+        <v>90000302</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A20" s="4">
+        <v>30005</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3</v>
+      </c>
+      <c r="C20" s="8">
+        <v>16001</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="F20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="2">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37527F98-E580-41C8-8CA2-7A830FC8ED65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7759A2B0-4DB7-4A2C-990F-FAABE2CBBB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="99">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -172,13 +172,196 @@
   <si>
     <t>10,4,40,8,100,12,200,16,300,20</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>守卫0（浮桥机关）</t>
+  </si>
+  <si>
+    <t>守卫1（黄钥匙）</t>
+  </si>
+  <si>
+    <t>黄门</t>
+  </si>
+  <si>
+    <t>守卫2（强化石）</t>
+  </si>
+  <si>
+    <t>强化石</t>
+  </si>
+  <si>
+    <t>石球机关</t>
+  </si>
+  <si>
+    <t>守卫2（石球）</t>
+  </si>
+  <si>
+    <t>守卫3（红钥匙）</t>
+  </si>
+  <si>
+    <t>守卫4（浮桥机关）</t>
+  </si>
+  <si>
+    <t>红门</t>
+  </si>
+  <si>
+    <t>推箱子门</t>
+  </si>
+  <si>
+    <t>守卫0（强化石）</t>
+  </si>
+  <si>
+    <t>强化石1</t>
+  </si>
+  <si>
+    <t>守卫1（炮弹）</t>
+  </si>
+  <si>
+    <t>大炮</t>
+  </si>
+  <si>
+    <t>土墙</t>
+  </si>
+  <si>
+    <t>金币1</t>
+  </si>
+  <si>
+    <t>守卫3（石球机关）</t>
+  </si>
+  <si>
+    <t>守卫4（火把）</t>
+  </si>
+  <si>
+    <t>刷怪区域2</t>
+  </si>
+  <si>
+    <t>武器1</t>
+  </si>
+  <si>
+    <t>守卫5（红钥匙）</t>
+  </si>
+  <si>
+    <t>金币2</t>
+  </si>
+  <si>
+    <t>守卫6（水壶）</t>
+  </si>
+  <si>
+    <t>守卫7（强化石）</t>
+  </si>
+  <si>
+    <t>强化石2</t>
+  </si>
+  <si>
+    <t>火门</t>
+  </si>
+  <si>
+    <t>守卫1</t>
+  </si>
+  <si>
+    <t>石墙</t>
+  </si>
+  <si>
+    <t>守卫2</t>
+  </si>
+  <si>
+    <t>守卫3（火把）</t>
+  </si>
+  <si>
+    <t>守卫4（绿钥匙）</t>
+  </si>
+  <si>
+    <t>绿门</t>
+  </si>
+  <si>
+    <t>护甲1</t>
+  </si>
+  <si>
+    <t>守卫5（推箱子）</t>
+  </si>
+  <si>
+    <t>守卫6（石球）</t>
+  </si>
+  <si>
+    <t>守卫7</t>
+  </si>
+  <si>
+    <t>守卫8（浮桥机关）</t>
+  </si>
+  <si>
+    <t>护甲2</t>
+  </si>
+  <si>
+    <t>守卫9</t>
+  </si>
+  <si>
+    <t>守卫10（大炮炮弹）</t>
+  </si>
+  <si>
+    <t>守卫11（护盾）</t>
+  </si>
+  <si>
+    <t>炸弹</t>
+  </si>
+  <si>
+    <t>守卫12（金币）</t>
+  </si>
+  <si>
+    <t>武器2</t>
+  </si>
+  <si>
+    <t>守卫13</t>
+  </si>
+  <si>
+    <t>守卫14（激光发射）</t>
+  </si>
+  <si>
+    <t>激光镜门</t>
+  </si>
+  <si>
+    <t>深坑</t>
+  </si>
+  <si>
+    <t>护甲3</t>
+  </si>
+  <si>
+    <t>守卫15（金币）</t>
+  </si>
+  <si>
+    <t>金币3</t>
+  </si>
+  <si>
+    <t>守卫16</t>
+  </si>
+  <si>
+    <t>守卫17（木头）</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>守卫18（梯子攀爬）</t>
+  </si>
+  <si>
+    <t>梯子攀爬</t>
+  </si>
+  <si>
+    <t>守卫19（强化石）</t>
+  </si>
+  <si>
+    <t>强化石3</t>
+  </si>
+  <si>
+    <t>武器3</t>
+  </si>
+  <si>
+    <t>刷怪区域3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,6 +399,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -264,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -287,6 +478,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -695,7 +892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -704,7 +901,7 @@
     <col min="4" max="4" width="11.625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="3"/>
     <col min="6" max="6" width="21.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.75" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
@@ -719,6 +916,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
@@ -888,6 +1086,7 @@
         <v>2001</v>
       </c>
       <c r="D8" s="8"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="8" t="s">
         <v>25</v>
       </c>
@@ -976,6 +1175,7 @@
       <c r="C12" s="8">
         <v>2001</v>
       </c>
+      <c r="D12" s="10"/>
       <c r="F12" s="8" t="s">
         <v>25</v>
       </c>
@@ -1083,7 +1283,6 @@
       <c r="F17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="2">
         <v>0</v>
@@ -1149,10 +1348,1631 @@
       <c r="F20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="2">
+      <c r="I20" s="4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A21" s="4">
+        <v>40001</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="8">
+        <v>5003</v>
+      </c>
+      <c r="D21" s="8">
+        <v>90000400</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A22" s="4">
+        <v>40002</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4</v>
+      </c>
+      <c r="C22" s="8">
+        <v>6001</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A23" s="4">
+        <v>40003</v>
+      </c>
+      <c r="B23" s="3">
+        <v>4</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2001</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A24" s="4">
+        <v>40004</v>
+      </c>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D24" s="8">
+        <v>90000401</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A25" s="4">
+        <v>40005</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="8">
+        <v>160001</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A26" s="4">
+        <v>40006</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D26" s="8">
+        <v>90000402</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A27" s="4">
+        <v>40007</v>
+      </c>
+      <c r="B27" s="3">
+        <v>4</v>
+      </c>
+      <c r="C27" s="8">
+        <v>72001</v>
+      </c>
+      <c r="E27" s="8">
+        <v>40001</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A28" s="4">
+        <v>40008</v>
+      </c>
+      <c r="B28" s="3">
+        <v>4</v>
+      </c>
+      <c r="C28" s="8">
+        <v>20001</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="F28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A29" s="4">
+        <v>50001</v>
+      </c>
+      <c r="B29" s="3">
+        <v>5</v>
+      </c>
+      <c r="C29" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D29" s="8">
+        <v>90000502</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A30" s="4">
+        <v>50002</v>
+      </c>
+      <c r="B30" s="3">
+        <v>5</v>
+      </c>
+      <c r="C30" s="8">
+        <v>20001</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A31" s="4">
+        <v>50003</v>
+      </c>
+      <c r="B31" s="3">
+        <v>5</v>
+      </c>
+      <c r="C31" s="8">
+        <v>28001</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="F31" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A32" s="4">
+        <v>50004</v>
+      </c>
+      <c r="B32" s="3">
+        <v>5</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2001</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A33" s="4">
+        <v>50005</v>
+      </c>
+      <c r="B33" s="3">
+        <v>5</v>
+      </c>
+      <c r="C33" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D33" s="8">
+        <v>90000503</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="10">
+        <v>2</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A34" s="4">
+        <v>50006</v>
+      </c>
+      <c r="B34" s="3">
+        <v>5</v>
+      </c>
+      <c r="C34" s="8">
+        <v>5003</v>
+      </c>
+      <c r="D34" s="8">
+        <v>90000504</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="10">
+        <v>2</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A35" s="4">
+        <v>50007</v>
+      </c>
+      <c r="B35" s="3">
+        <v>5</v>
+      </c>
+      <c r="C35" s="8">
+        <v>6001</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A36" s="4">
+        <v>50008</v>
+      </c>
+      <c r="B36" s="3">
+        <v>5</v>
+      </c>
+      <c r="C36" s="8">
+        <v>72001</v>
+      </c>
+      <c r="D36" s="10"/>
+      <c r="E36" s="8">
+        <v>50001</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A37" s="4">
+        <v>50009</v>
+      </c>
+      <c r="B37" s="3">
+        <v>5</v>
+      </c>
+      <c r="C37" s="8">
+        <v>16001</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A38" s="4">
+        <v>50010</v>
+      </c>
+      <c r="B38" s="3">
+        <v>5</v>
+      </c>
+      <c r="C38" s="8">
+        <v>16003</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A39" s="4">
+        <v>60001</v>
+      </c>
+      <c r="B39" s="3">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D39" s="8">
+        <v>90000601</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="10">
+        <v>2</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A40" s="4">
+        <v>60002</v>
+      </c>
+      <c r="B40" s="3">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8">
+        <v>72001</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8">
+        <v>60001</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A41" s="4">
+        <v>60003</v>
+      </c>
+      <c r="B41" s="3">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D41" s="8">
+        <v>90000602</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="10">
+        <v>2</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A42" s="4">
+        <v>60004</v>
+      </c>
+      <c r="B42" s="3">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>48001</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A43" s="4">
+        <v>60005</v>
+      </c>
+      <c r="B43" s="3">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>2001</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A44" s="4">
+        <v>60006</v>
+      </c>
+      <c r="B44" s="3">
+        <v>6</v>
+      </c>
+      <c r="C44" s="8">
+        <v>5004</v>
+      </c>
+      <c r="D44" s="8">
+        <v>90000603</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="10">
+        <v>2</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A45" s="4">
+        <v>60007</v>
+      </c>
+      <c r="B45" s="3">
+        <v>6</v>
+      </c>
+      <c r="C45" s="8">
+        <v>54001</v>
+      </c>
+      <c r="D45" s="10"/>
+      <c r="F45" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A46" s="4">
+        <v>60008</v>
+      </c>
+      <c r="B46" s="3">
+        <v>6</v>
+      </c>
+      <c r="C46" s="8">
+        <v>72002</v>
+      </c>
+      <c r="E46" s="8">
+        <v>60002</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A47" s="4">
+        <v>60009</v>
+      </c>
+      <c r="B47" s="3">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>5008</v>
+      </c>
+      <c r="D47" s="8">
+        <v>90000604</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="10">
+        <v>2</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A48" s="4">
+        <v>60010</v>
+      </c>
+      <c r="B48" s="3">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>20001</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A49" s="4">
+        <v>60011</v>
+      </c>
+      <c r="B49" s="3">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>16002</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A50" s="4">
+        <v>60012</v>
+      </c>
+      <c r="B50" s="3">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
+        <v>5003</v>
+      </c>
+      <c r="D50" s="8">
+        <v>90000605</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="10">
+        <v>2</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A51" s="4">
+        <v>60013</v>
+      </c>
+      <c r="B51" s="3">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>43001</v>
+      </c>
+      <c r="D51" s="10"/>
+      <c r="F51" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A52" s="4">
+        <v>60014</v>
+      </c>
+      <c r="B52" s="3">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>2003</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A53" s="4">
+        <v>60015</v>
+      </c>
+      <c r="B53" s="3">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>71001</v>
+      </c>
+      <c r="E53" s="8">
+        <v>60003</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A54" s="4">
+        <v>60016</v>
+      </c>
+      <c r="B54" s="3">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>5005</v>
+      </c>
+      <c r="D54" s="8">
+        <v>90000606</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G54" s="10">
+        <v>2</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A55" s="4">
+        <v>60017</v>
+      </c>
+      <c r="B55" s="3">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>16003</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="F55" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A56" s="4">
+        <v>60018</v>
+      </c>
+      <c r="B56" s="3">
+        <v>6</v>
+      </c>
+      <c r="C56" s="8">
+        <v>72004</v>
+      </c>
+      <c r="D56" s="10"/>
+      <c r="E56" s="8">
+        <v>60004</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A57" s="4">
+        <v>60019</v>
+      </c>
+      <c r="B57" s="3">
+        <v>6</v>
+      </c>
+      <c r="C57" s="8">
+        <v>5007</v>
+      </c>
+      <c r="D57" s="8">
+        <v>90000607</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="10">
+        <v>2</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A58" s="4">
+        <v>60020</v>
+      </c>
+      <c r="B58" s="3">
+        <v>6</v>
+      </c>
+      <c r="C58" s="8">
+        <v>5006</v>
+      </c>
+      <c r="D58" s="8">
+        <v>90000608</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G58" s="10">
+        <v>2</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A59" s="4">
+        <v>60021</v>
+      </c>
+      <c r="B59" s="3">
+        <v>6</v>
+      </c>
+      <c r="C59" s="8">
+        <v>72003</v>
+      </c>
+      <c r="E59" s="8">
+        <v>60005</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A60" s="4">
+        <v>60022</v>
+      </c>
+      <c r="B60" s="3">
+        <v>6</v>
+      </c>
+      <c r="C60" s="8">
+        <v>17001</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A61" s="4">
+        <v>60023</v>
+      </c>
+      <c r="B61" s="3">
+        <v>6</v>
+      </c>
+      <c r="C61" s="8">
+        <v>30001</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A62" s="4">
+        <v>70001</v>
+      </c>
+      <c r="B62" s="3">
+        <v>7</v>
+      </c>
+      <c r="C62" s="8">
+        <v>5015</v>
+      </c>
+      <c r="D62" s="8">
+        <v>90000701</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A63" s="4">
+        <v>70002</v>
+      </c>
+      <c r="B63" s="3">
+        <v>7</v>
+      </c>
+      <c r="C63" s="8">
+        <v>55001</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A64" s="4">
+        <v>70003</v>
+      </c>
+      <c r="B64" s="3">
+        <v>7</v>
+      </c>
+      <c r="C64" s="8">
+        <v>5014</v>
+      </c>
+      <c r="D64" s="8">
+        <v>90000702</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G64" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A65" s="4">
+        <v>70004</v>
+      </c>
+      <c r="B65" s="3">
+        <v>7</v>
+      </c>
+      <c r="C65" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D65" s="8">
+        <v>90000703</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A66" s="4">
+        <v>70005</v>
+      </c>
+      <c r="B66" s="3">
+        <v>7</v>
+      </c>
+      <c r="C66" s="8">
+        <v>5016</v>
+      </c>
+      <c r="D66" s="8">
+        <v>90000704</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A67" s="4">
+        <v>70006</v>
+      </c>
+      <c r="B67" s="3">
+        <v>7</v>
+      </c>
+      <c r="C67" s="8">
+        <v>16001</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A68" s="4">
+        <v>70007</v>
+      </c>
+      <c r="B68" s="3">
+        <v>7</v>
+      </c>
+      <c r="C68" s="8">
+        <v>66001</v>
+      </c>
+      <c r="E68" s="8">
+        <v>70001</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A69" s="4">
+        <v>70008</v>
+      </c>
+      <c r="B69" s="3">
+        <v>7</v>
+      </c>
+      <c r="C69" s="8">
+        <v>5019</v>
+      </c>
+      <c r="D69" s="8">
+        <v>90000705</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G69" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A70" s="4">
+        <v>70009</v>
+      </c>
+      <c r="B70" s="3">
+        <v>7</v>
+      </c>
+      <c r="C70" s="8">
+        <v>16003</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A71" s="4">
+        <v>70010</v>
+      </c>
+      <c r="B71" s="3">
+        <v>7</v>
+      </c>
+      <c r="C71" s="8">
+        <v>72003</v>
+      </c>
+      <c r="E71" s="8">
+        <v>70002</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A72" s="4">
+        <v>70011</v>
+      </c>
+      <c r="B72" s="3">
+        <v>7</v>
+      </c>
+      <c r="C72" s="8">
+        <v>5017</v>
+      </c>
+      <c r="D72" s="8">
+        <v>90000706</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A73" s="4">
+        <v>70012</v>
+      </c>
+      <c r="B73" s="3">
+        <v>7</v>
+      </c>
+      <c r="C73" s="8">
+        <v>20001</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A74" s="4">
+        <v>70013</v>
+      </c>
+      <c r="B74" s="3">
+        <v>7</v>
+      </c>
+      <c r="C74" s="8">
+        <v>72001</v>
+      </c>
+      <c r="E74" s="8">
+        <v>70003</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A75" s="4">
+        <v>70014</v>
+      </c>
+      <c r="B75" s="3">
+        <v>7</v>
+      </c>
+      <c r="C75" s="8">
+        <v>43001</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A76" s="4">
+        <v>70015</v>
+      </c>
+      <c r="B76" s="3">
+        <v>7</v>
+      </c>
+      <c r="C76" s="8">
+        <v>71001</v>
+      </c>
+      <c r="E76" s="8">
+        <v>70004</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A77" s="4">
+        <v>70016</v>
+      </c>
+      <c r="B77" s="3">
+        <v>7</v>
+      </c>
+      <c r="C77" s="8">
+        <v>2001</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A78" s="4">
+        <v>70017</v>
+      </c>
+      <c r="B78" s="3">
+        <v>7</v>
+      </c>
+      <c r="C78" s="8">
+        <v>5012</v>
+      </c>
+      <c r="D78" s="8">
+        <v>90000707</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G78" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A79" s="4">
+        <v>70018</v>
+      </c>
+      <c r="B79" s="3">
+        <v>7</v>
+      </c>
+      <c r="C79" s="8">
+        <v>5011</v>
+      </c>
+      <c r="D79" s="8">
+        <v>90000708</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A80" s="4">
+        <v>70019</v>
+      </c>
+      <c r="B80" s="3">
+        <v>7</v>
+      </c>
+      <c r="C80" s="8">
+        <v>6001</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A81" s="4">
+        <v>70020</v>
+      </c>
+      <c r="B81" s="3">
+        <v>7</v>
+      </c>
+      <c r="C81" s="8">
+        <v>66002</v>
+      </c>
+      <c r="E81" s="8">
+        <v>70005</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A82" s="4">
+        <v>70021</v>
+      </c>
+      <c r="B82" s="3">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8">
+        <v>5013</v>
+      </c>
+      <c r="D82" s="8">
+        <v>90000709</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A83" s="4">
+        <v>70022</v>
+      </c>
+      <c r="B83" s="3">
+        <v>7</v>
+      </c>
+      <c r="C83" s="8">
+        <v>5018</v>
+      </c>
+      <c r="D83" s="8">
+        <v>90000710</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G83" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A84" s="4">
+        <v>70023</v>
+      </c>
+      <c r="B84" s="3">
+        <v>7</v>
+      </c>
+      <c r="C84" s="8">
+        <v>48001</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A85" s="4">
+        <v>70024</v>
+      </c>
+      <c r="B85" s="3">
+        <v>7</v>
+      </c>
+      <c r="C85" s="8">
+        <v>5010</v>
+      </c>
+      <c r="D85" s="8">
+        <v>90000711</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G85" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A86" s="4">
+        <v>70025</v>
+      </c>
+      <c r="B86" s="3">
+        <v>7</v>
+      </c>
+      <c r="C86" s="8">
+        <v>10001</v>
+      </c>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A87" s="4">
+        <v>70026</v>
+      </c>
+      <c r="B87" s="3">
+        <v>7</v>
+      </c>
+      <c r="C87" s="8">
+        <v>72002</v>
+      </c>
+      <c r="E87" s="8">
+        <v>70006</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A88" s="4">
+        <v>70027</v>
+      </c>
+      <c r="B88" s="3">
+        <v>7</v>
+      </c>
+      <c r="C88" s="8">
+        <v>5008</v>
+      </c>
+      <c r="D88" s="8">
+        <v>90000712</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G88" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A89" s="4">
+        <v>70028</v>
+      </c>
+      <c r="B89" s="3">
+        <v>7</v>
+      </c>
+      <c r="C89" s="8">
+        <v>72004</v>
+      </c>
+      <c r="E89" s="8">
+        <v>70007</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A90" s="4">
+        <v>70029</v>
+      </c>
+      <c r="B90" s="3">
+        <v>7</v>
+      </c>
+      <c r="C90" s="8">
+        <v>71002</v>
+      </c>
+      <c r="E90" s="8">
+        <v>70008</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A91" s="4">
+        <v>70030</v>
+      </c>
+      <c r="B91" s="3">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8">
+        <v>2003</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G91" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A92" s="4">
+        <v>70031</v>
+      </c>
+      <c r="B92" s="3">
+        <v>7</v>
+      </c>
+      <c r="C92" s="8">
+        <v>5006</v>
+      </c>
+      <c r="D92" s="8">
+        <v>90000713</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G92" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A93" s="4">
+        <v>70032</v>
+      </c>
+      <c r="B93" s="3">
+        <v>7</v>
+      </c>
+      <c r="C93" s="8">
+        <v>5005</v>
+      </c>
+      <c r="D93" s="8">
+        <v>90000714</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G93" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A94" s="4">
+        <v>70033</v>
+      </c>
+      <c r="B94" s="3">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8">
+        <v>16005</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A95" s="4">
+        <v>70034</v>
+      </c>
+      <c r="B95" s="3">
+        <v>7</v>
+      </c>
+      <c r="C95" s="8">
+        <v>41001</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A96" s="4">
+        <v>70035</v>
+      </c>
+      <c r="B96" s="3">
+        <v>7</v>
+      </c>
+      <c r="C96" s="8">
+        <v>66003</v>
+      </c>
+      <c r="E96" s="8">
+        <v>70009</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A97" s="4">
+        <v>70036</v>
+      </c>
+      <c r="B97" s="3">
+        <v>7</v>
+      </c>
+      <c r="C97" s="8">
+        <v>5007</v>
+      </c>
+      <c r="D97" s="8">
+        <v>90000715</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G97" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A98" s="4">
+        <v>70037</v>
+      </c>
+      <c r="B98" s="3">
+        <v>7</v>
+      </c>
+      <c r="C98" s="8">
+        <v>66004</v>
+      </c>
+      <c r="E98" s="8">
+        <v>70011</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A99" s="4">
+        <v>70038</v>
+      </c>
+      <c r="B99" s="3">
+        <v>7</v>
+      </c>
+      <c r="C99" s="8">
+        <v>5004</v>
+      </c>
+      <c r="D99" s="8">
+        <v>90000716</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G99" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A100" s="4">
+        <v>70039</v>
+      </c>
+      <c r="B100" s="3">
+        <v>7</v>
+      </c>
+      <c r="C100" s="8">
+        <v>5003</v>
+      </c>
+      <c r="D100" s="8">
+        <v>90000717</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G100" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A101" s="4">
+        <v>70040</v>
+      </c>
+      <c r="B101" s="3">
+        <v>7</v>
+      </c>
+      <c r="C101" s="8">
+        <v>28001</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A102" s="4">
+        <v>70041</v>
+      </c>
+      <c r="B102" s="3">
+        <v>7</v>
+      </c>
+      <c r="C102" s="8">
+        <v>21001</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A103" s="4">
+        <v>70042</v>
+      </c>
+      <c r="B103" s="3">
+        <v>7</v>
+      </c>
+      <c r="C103" s="8">
+        <v>30001</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A104" s="4">
+        <v>70043</v>
+      </c>
+      <c r="B104" s="3">
+        <v>7</v>
+      </c>
+      <c r="C104" s="8">
+        <v>5009</v>
+      </c>
+      <c r="D104" s="8">
+        <v>90000718</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G104" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A105" s="4">
+        <v>70044</v>
+      </c>
+      <c r="B105" s="3">
+        <v>7</v>
+      </c>
+      <c r="C105" s="8">
+        <v>9001</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A106" s="4">
+        <v>70045</v>
+      </c>
+      <c r="B106" s="3">
+        <v>7</v>
+      </c>
+      <c r="C106" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D106" s="8">
+        <v>90000719</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G106" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A107" s="4">
+        <v>70046</v>
+      </c>
+      <c r="B107" s="3">
+        <v>7</v>
+      </c>
+      <c r="C107" s="8">
+        <v>72005</v>
+      </c>
+      <c r="E107" s="8">
+        <v>70012</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A108" s="4">
+        <v>70047</v>
+      </c>
+      <c r="B108" s="3">
+        <v>7</v>
+      </c>
+      <c r="C108" s="8">
+        <v>17001</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A109" s="4">
+        <v>70048</v>
+      </c>
+      <c r="B109" s="3">
+        <v>7</v>
+      </c>
+      <c r="C109" s="8">
+        <v>71003</v>
+      </c>
+      <c r="E109" s="8">
+        <v>70013</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A110" s="4">
+        <v>70049</v>
+      </c>
+      <c r="B110" s="3">
+        <v>7</v>
+      </c>
+      <c r="C110" s="8">
+        <v>2009</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G110" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7759A2B0-4DB7-4A2C-990F-FAABE2CBBB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8CBDC6-75A6-4567-B184-813E3917AAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -126,9 +126,6 @@
     <t>守卫1（火把）</t>
   </si>
   <si>
-    <t>火把</t>
-  </si>
-  <si>
     <t>藤蔓吊桥</t>
   </si>
   <si>
@@ -170,191 +167,199 @@
     <t>守卫2（蓝钥匙）</t>
   </si>
   <si>
-    <t>10,4,40,8,100,12,200,16,300,20</t>
+    <t>守卫0（浮桥机关）</t>
+  </si>
+  <si>
+    <t>守卫1（黄钥匙）</t>
+  </si>
+  <si>
+    <t>黄门</t>
+  </si>
+  <si>
+    <t>守卫2（强化石）</t>
+  </si>
+  <si>
+    <t>强化石</t>
+  </si>
+  <si>
+    <t>石球机关</t>
+  </si>
+  <si>
+    <t>守卫2（石球）</t>
+  </si>
+  <si>
+    <t>守卫3（红钥匙）</t>
+  </si>
+  <si>
+    <t>守卫4（浮桥机关）</t>
+  </si>
+  <si>
+    <t>红门</t>
+  </si>
+  <si>
+    <t>推箱子门</t>
+  </si>
+  <si>
+    <t>守卫0（强化石）</t>
+  </si>
+  <si>
+    <t>强化石1</t>
+  </si>
+  <si>
+    <t>守卫1（炮弹）</t>
+  </si>
+  <si>
+    <t>大炮</t>
+  </si>
+  <si>
+    <t>土墙</t>
+  </si>
+  <si>
+    <t>金币1</t>
+  </si>
+  <si>
+    <t>守卫3（石球机关）</t>
+  </si>
+  <si>
+    <t>守卫4（火把）</t>
+  </si>
+  <si>
+    <t>刷怪区域2</t>
+  </si>
+  <si>
+    <t>武器1</t>
+  </si>
+  <si>
+    <t>守卫5（红钥匙）</t>
+  </si>
+  <si>
+    <t>金币2</t>
+  </si>
+  <si>
+    <t>守卫6（水壶）</t>
+  </si>
+  <si>
+    <t>守卫7（强化石）</t>
+  </si>
+  <si>
+    <t>强化石2</t>
+  </si>
+  <si>
+    <t>火门</t>
+  </si>
+  <si>
+    <t>守卫1</t>
+  </si>
+  <si>
+    <t>石墙</t>
+  </si>
+  <si>
+    <t>守卫2</t>
+  </si>
+  <si>
+    <t>守卫3（火把）</t>
+  </si>
+  <si>
+    <t>守卫4（绿钥匙）</t>
+  </si>
+  <si>
+    <t>绿门</t>
+  </si>
+  <si>
+    <t>护甲1</t>
+  </si>
+  <si>
+    <t>守卫5（推箱子）</t>
+  </si>
+  <si>
+    <t>守卫6（石球）</t>
+  </si>
+  <si>
+    <t>守卫7</t>
+  </si>
+  <si>
+    <t>守卫8（浮桥机关）</t>
+  </si>
+  <si>
+    <t>护甲2</t>
+  </si>
+  <si>
+    <t>守卫9</t>
+  </si>
+  <si>
+    <t>守卫10（大炮炮弹）</t>
+  </si>
+  <si>
+    <t>守卫11（护盾）</t>
+  </si>
+  <si>
+    <t>炸弹</t>
+  </si>
+  <si>
+    <t>守卫12（金币）</t>
+  </si>
+  <si>
+    <t>武器2</t>
+  </si>
+  <si>
+    <t>守卫13</t>
+  </si>
+  <si>
+    <t>守卫14（激光发射）</t>
+  </si>
+  <si>
+    <t>激光镜门</t>
+  </si>
+  <si>
+    <t>深坑</t>
+  </si>
+  <si>
+    <t>护甲3</t>
+  </si>
+  <si>
+    <t>守卫15（金币）</t>
+  </si>
+  <si>
+    <t>金币3</t>
+  </si>
+  <si>
+    <t>守卫16</t>
+  </si>
+  <si>
+    <t>守卫17（木头）</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>守卫18（梯子攀爬）</t>
+  </si>
+  <si>
+    <t>梯子攀爬</t>
+  </si>
+  <si>
+    <t>守卫19（强化石）</t>
+  </si>
+  <si>
+    <t>强化石3</t>
+  </si>
+  <si>
+    <t>武器3</t>
+  </si>
+  <si>
+    <t>刷怪区域3</t>
+  </si>
+  <si>
+    <t>10,10,30,20,60,30,100,40,150,60,210,80,300,100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>守卫0（浮桥机关）</t>
-  </si>
-  <si>
-    <t>守卫1（黄钥匙）</t>
-  </si>
-  <si>
-    <t>黄门</t>
-  </si>
-  <si>
-    <t>守卫2（强化石）</t>
-  </si>
-  <si>
-    <t>强化石</t>
-  </si>
-  <si>
-    <t>石球机关</t>
-  </si>
-  <si>
-    <t>守卫2（石球）</t>
-  </si>
-  <si>
-    <t>守卫3（红钥匙）</t>
-  </si>
-  <si>
-    <t>守卫4（浮桥机关）</t>
-  </si>
-  <si>
-    <t>红门</t>
-  </si>
-  <si>
-    <t>推箱子门</t>
-  </si>
-  <si>
-    <t>守卫0（强化石）</t>
-  </si>
-  <si>
-    <t>强化石1</t>
-  </si>
-  <si>
-    <t>守卫1（炮弹）</t>
-  </si>
-  <si>
-    <t>大炮</t>
-  </si>
-  <si>
-    <t>土墙</t>
-  </si>
-  <si>
-    <t>金币1</t>
-  </si>
-  <si>
-    <t>守卫3（石球机关）</t>
-  </si>
-  <si>
-    <t>守卫4（火把）</t>
-  </si>
-  <si>
-    <t>刷怪区域2</t>
-  </si>
-  <si>
-    <t>武器1</t>
-  </si>
-  <si>
-    <t>守卫5（红钥匙）</t>
-  </si>
-  <si>
-    <t>金币2</t>
-  </si>
-  <si>
-    <t>守卫6（水壶）</t>
-  </si>
-  <si>
-    <t>守卫7（强化石）</t>
-  </si>
-  <si>
-    <t>强化石2</t>
-  </si>
-  <si>
-    <t>火门</t>
-  </si>
-  <si>
-    <t>守卫1</t>
-  </si>
-  <si>
-    <t>石墙</t>
-  </si>
-  <si>
-    <t>守卫2</t>
-  </si>
-  <si>
-    <t>守卫3（火把）</t>
-  </si>
-  <si>
-    <t>守卫4（绿钥匙）</t>
-  </si>
-  <si>
-    <t>绿门</t>
-  </si>
-  <si>
-    <t>护甲1</t>
-  </si>
-  <si>
-    <t>守卫5（推箱子）</t>
-  </si>
-  <si>
-    <t>守卫6（石球）</t>
-  </si>
-  <si>
-    <t>守卫7</t>
-  </si>
-  <si>
-    <t>守卫8（浮桥机关）</t>
-  </si>
-  <si>
-    <t>护甲2</t>
-  </si>
-  <si>
-    <t>守卫9</t>
-  </si>
-  <si>
-    <t>守卫10（大炮炮弹）</t>
-  </si>
-  <si>
-    <t>守卫11（护盾）</t>
-  </si>
-  <si>
-    <t>炸弹</t>
-  </si>
-  <si>
-    <t>守卫12（金币）</t>
-  </si>
-  <si>
-    <t>武器2</t>
-  </si>
-  <si>
-    <t>守卫13</t>
-  </si>
-  <si>
-    <t>守卫14（激光发射）</t>
-  </si>
-  <si>
-    <t>激光镜门</t>
-  </si>
-  <si>
-    <t>深坑</t>
-  </si>
-  <si>
-    <t>护甲3</t>
-  </si>
-  <si>
-    <t>守卫15（金币）</t>
-  </si>
-  <si>
-    <t>金币3</t>
-  </si>
-  <si>
-    <t>守卫16</t>
-  </si>
-  <si>
-    <t>守卫17（木头）</t>
-  </si>
-  <si>
-    <t>岩浆球</t>
-  </si>
-  <si>
-    <t>守卫18（梯子攀爬）</t>
-  </si>
-  <si>
-    <t>梯子攀爬</t>
-  </si>
-  <si>
-    <t>守卫19（强化石）</t>
-  </si>
-  <si>
-    <t>强化石3</t>
-  </si>
-  <si>
-    <t>武器3</t>
-  </si>
-  <si>
-    <t>刷怪区域3</t>
+    <t>10,20,30,40,60,60,100,80,150,120,210,160,300,200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,10,60,20,120,30,200,40,300,60,420,80,560,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -480,10 +485,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -509,14 +514,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -557,13 +562,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -892,7 +897,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -902,7 +907,7 @@
     <col min="5" max="5" width="9" style="3"/>
     <col min="6" max="6" width="21.625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.375" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.75" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
@@ -917,6 +922,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
@@ -964,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -993,7 +999,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -1025,7 +1031,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
@@ -1039,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="8">
-        <v>44001</v>
+        <v>43001</v>
       </c>
       <c r="D6" s="8"/>
       <c r="F6" s="8" t="s">
@@ -1047,7 +1053,7 @@
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="3">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -1061,18 +1067,17 @@
         <v>1</v>
       </c>
       <c r="C7" s="8">
-        <v>43001</v>
+        <v>2001</v>
       </c>
       <c r="D7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="3">
-        <v>8</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
+      <c r="G7" s="8">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -1083,42 +1088,45 @@
         <v>1</v>
       </c>
       <c r="C8" s="8">
-        <v>2001</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10"/>
+        <v>5001</v>
+      </c>
+      <c r="D8" s="9">
+        <v>90000102</v>
+      </c>
       <c r="F8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="8">
-        <v>2</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
-        <v>10005</v>
+        <v>20001</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="8">
         <v>5001</v>
       </c>
-      <c r="D9" s="9">
-        <v>90000102</v>
+      <c r="D9" s="8">
+        <v>90000201</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -1126,1853 +1134,1968 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
       </c>
       <c r="C10" s="8">
-        <v>5001</v>
-      </c>
-      <c r="D10" s="8">
-        <v>90000201</v>
+        <v>16001</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="G10" s="8"/>
+      <c r="H10" s="3">
+        <v>50</v>
+      </c>
+      <c r="I10" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
-        <v>20002</v>
+        <v>20003</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
       </c>
       <c r="C11" s="8">
-        <v>16001</v>
+        <v>2001</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="I11" s="2">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="G11" s="8">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
-        <v>20003</v>
+        <v>20004</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
       </c>
       <c r="C12" s="8">
-        <v>2001</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>5002</v>
+      </c>
+      <c r="D12" s="8">
+        <v>90000202</v>
+      </c>
+      <c r="E12"/>
       <c r="F12" s="8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G12" s="8">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
-        <v>20004</v>
+        <v>20005</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
       </c>
       <c r="C13" s="8">
-        <v>5002</v>
-      </c>
-      <c r="D13" s="8">
-        <v>90000202</v>
-      </c>
-      <c r="E13"/>
+        <v>6001</v>
+      </c>
       <c r="F13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="G13" s="8"/>
+      <c r="H13" s="3">
+        <v>50</v>
+      </c>
+      <c r="I13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
-        <v>20005</v>
+        <v>20006</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
       </c>
       <c r="C14" s="8">
-        <v>6001</v>
+        <v>17001</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="I14" s="2">
+      <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
-        <v>20006</v>
+        <v>30001</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="8">
-        <v>17001</v>
+        <v>5001</v>
+      </c>
+      <c r="D15" s="8">
+        <v>90000301</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="2">
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
       </c>
       <c r="C16" s="8">
-        <v>5001</v>
-      </c>
-      <c r="D16" s="8">
-        <v>90000301</v>
-      </c>
+        <v>28001</v>
+      </c>
+      <c r="D16" s="8"/>
       <c r="F16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="2">
+      <c r="H16" s="3">
+        <v>100</v>
+      </c>
+      <c r="I16" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
-        <v>30002</v>
+        <v>30003</v>
       </c>
       <c r="B17" s="3">
         <v>3</v>
       </c>
       <c r="C17" s="8">
-        <v>28001</v>
+        <v>2001</v>
       </c>
       <c r="D17" s="8"/>
       <c r="F17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="2">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
-        <v>30003</v>
+        <v>30004</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
       </c>
       <c r="C18" s="8">
-        <v>2001</v>
-      </c>
-      <c r="D18" s="8"/>
+        <v>5001</v>
+      </c>
+      <c r="D18" s="8">
+        <v>90000302</v>
+      </c>
       <c r="F18" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G18" s="3">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>100</v>
+      </c>
+      <c r="I18" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
-        <v>30004</v>
+        <v>30005</v>
       </c>
       <c r="B19" s="3">
         <v>3</v>
       </c>
       <c r="C19" s="8">
-        <v>5001</v>
-      </c>
-      <c r="D19" s="8">
-        <v>90000302</v>
-      </c>
+        <v>16001</v>
+      </c>
+      <c r="D19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="3">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2">
+        <v>29</v>
+      </c>
+      <c r="H19" s="3">
+        <v>200</v>
+      </c>
+      <c r="I19" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
-        <v>30005</v>
+        <v>40001</v>
       </c>
       <c r="B20" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="8">
-        <v>16001</v>
-      </c>
-      <c r="D20" s="8"/>
+        <v>5003</v>
+      </c>
+      <c r="D20" s="8">
+        <v>90000400</v>
+      </c>
       <c r="F20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="4">
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
-        <v>40001</v>
+        <v>40002</v>
       </c>
       <c r="B21" s="3">
         <v>4</v>
       </c>
       <c r="C21" s="8">
-        <v>5003</v>
-      </c>
-      <c r="D21" s="8">
-        <v>90000400</v>
+        <v>6001</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="H21" s="3">
+        <v>100</v>
+      </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
-        <v>40002</v>
+        <v>40003</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
       </c>
       <c r="C22" s="8">
-        <v>6001</v>
+        <v>2001</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="B23" s="3">
         <v>4</v>
       </c>
       <c r="C23" s="8">
-        <v>2001</v>
-      </c>
-      <c r="E23" s="10"/>
+        <v>5002</v>
+      </c>
+      <c r="D23" s="8">
+        <v>90000401</v>
+      </c>
       <c r="F23" s="8" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G23" s="3">
-        <v>3</v>
-      </c>
-      <c r="H23" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>100</v>
+      </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
-        <v>40004</v>
+        <v>40005</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="8">
-        <v>5002</v>
-      </c>
-      <c r="D24" s="8">
-        <v>90000401</v>
+        <v>160001</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
-        <v>40005</v>
+        <v>40006</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="8">
-        <v>160001</v>
+        <v>5001</v>
+      </c>
+      <c r="D25" s="8">
+        <v>90000402</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
-        <v>40006</v>
+        <v>40007</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
       </c>
       <c r="C26" s="8">
-        <v>5001</v>
-      </c>
-      <c r="D26" s="8">
-        <v>90000402</v>
+        <v>72001</v>
+      </c>
+      <c r="E26" s="8">
+        <v>40001</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1</v>
-      </c>
-      <c r="H26" s="4"/>
+        <v>40</v>
+      </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
-        <v>40007</v>
+        <v>40008</v>
       </c>
       <c r="B27" s="3">
         <v>4</v>
       </c>
       <c r="C27" s="8">
-        <v>72001</v>
-      </c>
-      <c r="E27" s="8">
-        <v>40001</v>
+        <v>20001</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="H27" s="3">
+        <v>200</v>
+      </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
-        <v>40008</v>
+        <v>50001</v>
       </c>
       <c r="B28" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" s="8">
-        <v>20001</v>
-      </c>
-      <c r="D28" s="10"/>
+        <v>5002</v>
+      </c>
+      <c r="D28" s="8">
+        <v>90000502</v>
+      </c>
       <c r="F28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
+        <v>100</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
-        <v>50001</v>
+        <v>50002</v>
       </c>
       <c r="B29" s="3">
         <v>5</v>
       </c>
       <c r="C29" s="8">
-        <v>5002</v>
-      </c>
-      <c r="D29" s="8">
-        <v>90000502</v>
+        <v>20001</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="3">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="H29" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
-        <v>50002</v>
+        <v>50003</v>
       </c>
       <c r="B30" s="3">
         <v>5</v>
       </c>
       <c r="C30" s="8">
-        <v>20001</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
+        <v>28001</v>
+      </c>
       <c r="F30" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="H30" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
-        <v>50003</v>
+        <v>50004</v>
       </c>
       <c r="B31" s="3">
         <v>5</v>
       </c>
       <c r="C31" s="8">
-        <v>28001</v>
-      </c>
-      <c r="D31" s="10"/>
+        <v>2001</v>
+      </c>
       <c r="F31" s="8" t="s">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="G31" s="3">
+        <v>3</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
-        <v>50004</v>
+        <v>50005</v>
       </c>
       <c r="B32" s="3">
         <v>5</v>
       </c>
       <c r="C32" s="8">
-        <v>2001</v>
+        <v>5001</v>
+      </c>
+      <c r="D32" s="8">
+        <v>90000503</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G32" s="3">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" s="4">
-        <v>50005</v>
+        <v>50006</v>
       </c>
       <c r="B33" s="3">
         <v>5</v>
       </c>
       <c r="C33" s="8">
-        <v>5001</v>
+        <v>5003</v>
       </c>
       <c r="D33" s="8">
-        <v>90000503</v>
+        <v>90000504</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="10">
+        <v>44</v>
+      </c>
+      <c r="G33" s="3">
         <v>2</v>
       </c>
-      <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="4">
-        <v>50006</v>
+        <v>50007</v>
       </c>
       <c r="B34" s="3">
         <v>5</v>
       </c>
       <c r="C34" s="8">
-        <v>5003</v>
-      </c>
-      <c r="D34" s="8">
-        <v>90000504</v>
+        <v>6001</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G34" s="10">
-        <v>2</v>
-      </c>
-      <c r="H34" s="4"/>
+        <v>31</v>
+      </c>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
-        <v>50007</v>
+        <v>50008</v>
       </c>
       <c r="B35" s="3">
         <v>5</v>
       </c>
       <c r="C35" s="8">
-        <v>6001</v>
+        <v>72001</v>
+      </c>
+      <c r="E35" s="8">
+        <v>50001</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="4"/>
+        <v>40</v>
+      </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
-        <v>50008</v>
+        <v>50009</v>
       </c>
       <c r="B36" s="3">
         <v>5</v>
       </c>
       <c r="C36" s="8">
-        <v>72001</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="8">
-        <v>50001</v>
+        <v>16001</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="H36" s="3">
+        <v>100</v>
+      </c>
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
-        <v>50009</v>
+        <v>50010</v>
       </c>
       <c r="B37" s="3">
         <v>5</v>
       </c>
       <c r="C37" s="8">
-        <v>16001</v>
+        <v>16003</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="H37" s="3">
+        <v>100</v>
+      </c>
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
-        <v>50010</v>
+        <v>60001</v>
       </c>
       <c r="B38" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="8">
-        <v>16003</v>
-      </c>
-      <c r="E38" s="10"/>
+        <v>5002</v>
+      </c>
+      <c r="D38" s="8">
+        <v>90000601</v>
+      </c>
       <c r="F38" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="G38" s="3">
+        <v>2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>50</v>
+      </c>
       <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
-        <v>60001</v>
+        <v>60002</v>
       </c>
       <c r="B39" s="3">
         <v>6</v>
       </c>
       <c r="C39" s="8">
-        <v>5002</v>
-      </c>
-      <c r="D39" s="8">
-        <v>90000601</v>
+        <v>72001</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8">
+        <v>60001</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G39" s="10">
-        <v>2</v>
-      </c>
-      <c r="H39" s="4"/>
+        <v>48</v>
+      </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
-        <v>60002</v>
+        <v>60003</v>
       </c>
       <c r="B40" s="3">
         <v>6</v>
       </c>
       <c r="C40" s="8">
-        <v>72001</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8">
-        <v>60001</v>
+        <v>5001</v>
+      </c>
+      <c r="D40" s="8">
+        <v>90000602</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H40" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G40" s="3">
+        <v>2</v>
+      </c>
+      <c r="H40" s="3">
+        <v>50</v>
+      </c>
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
-        <v>60003</v>
+        <v>60004</v>
       </c>
       <c r="B41" s="3">
         <v>6</v>
       </c>
       <c r="C41" s="8">
-        <v>5001</v>
-      </c>
-      <c r="D41" s="8">
-        <v>90000602</v>
+        <v>48001</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" s="10">
-        <v>2</v>
-      </c>
-      <c r="H41" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="H41" s="3">
+        <v>50</v>
+      </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
-        <v>60004</v>
+        <v>60005</v>
       </c>
       <c r="B42" s="3">
         <v>6</v>
       </c>
       <c r="C42" s="8">
-        <v>48001</v>
+        <v>2001</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="G42" s="3">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="4">
-        <v>60005</v>
+        <v>60006</v>
       </c>
       <c r="B43" s="3">
         <v>6</v>
       </c>
       <c r="C43" s="8">
-        <v>2001</v>
+        <v>5004</v>
+      </c>
+      <c r="D43" s="8">
+        <v>90000603</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G43" s="3">
-        <v>3</v>
-      </c>
-      <c r="H43" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="H43" s="3">
+        <v>50</v>
+      </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
-        <v>60006</v>
+        <v>60007</v>
       </c>
       <c r="B44" s="3">
         <v>6</v>
       </c>
       <c r="C44" s="8">
-        <v>5004</v>
-      </c>
-      <c r="D44" s="8">
-        <v>90000603</v>
+        <v>54001</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="10">
-        <v>2</v>
-      </c>
-      <c r="H44" s="4"/>
+        <v>51</v>
+      </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="4">
-        <v>60007</v>
+        <v>60008</v>
       </c>
       <c r="B45" s="3">
         <v>6</v>
       </c>
       <c r="C45" s="8">
-        <v>54001</v>
-      </c>
-      <c r="D45" s="10"/>
+        <v>72002</v>
+      </c>
+      <c r="E45" s="8">
+        <v>60002</v>
+      </c>
       <c r="F45" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H45" s="4"/>
+        <v>52</v>
+      </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="4">
-        <v>60008</v>
+        <v>60009</v>
       </c>
       <c r="B46" s="3">
         <v>6</v>
       </c>
       <c r="C46" s="8">
-        <v>72002</v>
-      </c>
-      <c r="E46" s="8">
-        <v>60002</v>
+        <v>5008</v>
+      </c>
+      <c r="D46" s="8">
+        <v>90000604</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H46" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2</v>
+      </c>
+      <c r="H46" s="3">
+        <v>50</v>
+      </c>
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="4">
-        <v>60009</v>
+        <v>60010</v>
       </c>
       <c r="B47" s="3">
         <v>6</v>
       </c>
       <c r="C47" s="8">
-        <v>5008</v>
-      </c>
-      <c r="D47" s="8">
-        <v>90000604</v>
+        <v>20001</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G47" s="10">
-        <v>2</v>
-      </c>
-      <c r="H47" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="H47" s="3">
+        <v>50</v>
+      </c>
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
-        <v>60010</v>
+        <v>60011</v>
       </c>
       <c r="B48" s="3">
         <v>6</v>
       </c>
       <c r="C48" s="8">
-        <v>20001</v>
+        <v>16002</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H48" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="H48" s="3">
+        <v>50</v>
+      </c>
       <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
-        <v>60011</v>
+        <v>60012</v>
       </c>
       <c r="B49" s="3">
         <v>6</v>
       </c>
       <c r="C49" s="8">
-        <v>16002</v>
-      </c>
-      <c r="E49" s="10"/>
+        <v>5003</v>
+      </c>
+      <c r="D49" s="8">
+        <v>90000605</v>
+      </c>
       <c r="F49" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H49" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2</v>
+      </c>
+      <c r="H49" s="3">
+        <v>50</v>
+      </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="4">
-        <v>60012</v>
+        <v>60013</v>
       </c>
       <c r="B50" s="3">
         <v>6</v>
       </c>
       <c r="C50" s="8">
-        <v>5003</v>
-      </c>
-      <c r="D50" s="8">
-        <v>90000605</v>
+        <v>43001</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G50" s="10">
-        <v>2</v>
-      </c>
-      <c r="H50" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="H50" s="3">
+        <v>50</v>
+      </c>
       <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
-        <v>60013</v>
+        <v>60014</v>
       </c>
       <c r="B51" s="3">
         <v>6</v>
       </c>
       <c r="C51" s="8">
-        <v>43001</v>
-      </c>
-      <c r="D51" s="10"/>
+        <v>2003</v>
+      </c>
       <c r="F51" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="G51" s="3">
+        <v>4</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
-        <v>60014</v>
+        <v>60015</v>
       </c>
       <c r="B52" s="3">
         <v>6</v>
       </c>
       <c r="C52" s="8">
-        <v>2003</v>
+        <v>71001</v>
+      </c>
+      <c r="E52" s="8">
+        <v>60003</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4</v>
-      </c>
-      <c r="H52" s="4"/>
+        <v>56</v>
+      </c>
       <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="4">
-        <v>60015</v>
+        <v>60016</v>
       </c>
       <c r="B53" s="3">
         <v>6</v>
       </c>
       <c r="C53" s="8">
-        <v>71001</v>
-      </c>
-      <c r="E53" s="8">
-        <v>60003</v>
+        <v>5005</v>
+      </c>
+      <c r="D53" s="8">
+        <v>90000606</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H53" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2</v>
+      </c>
+      <c r="H53" s="3">
+        <v>50</v>
+      </c>
       <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A54" s="4">
-        <v>60016</v>
+        <v>60017</v>
       </c>
       <c r="B54" s="3">
         <v>6</v>
       </c>
       <c r="C54" s="8">
-        <v>5005</v>
-      </c>
-      <c r="D54" s="8">
-        <v>90000606</v>
+        <v>16003</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G54" s="10">
-        <v>2</v>
-      </c>
-      <c r="H54" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="H54" s="3">
+        <v>50</v>
+      </c>
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A55" s="4">
-        <v>60017</v>
+        <v>60018</v>
       </c>
       <c r="B55" s="3">
         <v>6</v>
       </c>
       <c r="C55" s="8">
-        <v>16003</v>
-      </c>
-      <c r="D55" s="10"/>
+        <v>72004</v>
+      </c>
+      <c r="E55" s="8">
+        <v>60004</v>
+      </c>
       <c r="F55" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H55" s="4"/>
+        <v>58</v>
+      </c>
       <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
-        <v>60018</v>
+        <v>60019</v>
       </c>
       <c r="B56" s="3">
         <v>6</v>
       </c>
       <c r="C56" s="8">
-        <v>72004</v>
-      </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="8">
-        <v>60004</v>
+        <v>5007</v>
+      </c>
+      <c r="D56" s="8">
+        <v>90000607</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H56" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="G56" s="3">
+        <v>2</v>
+      </c>
+      <c r="H56" s="3">
+        <v>50</v>
+      </c>
       <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="4">
-        <v>60019</v>
+        <v>60020</v>
       </c>
       <c r="B57" s="3">
         <v>6</v>
       </c>
       <c r="C57" s="8">
-        <v>5007</v>
+        <v>5006</v>
       </c>
       <c r="D57" s="8">
-        <v>90000607</v>
+        <v>90000608</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G57" s="10">
+        <v>60</v>
+      </c>
+      <c r="G57" s="3">
         <v>2</v>
       </c>
-      <c r="H57" s="4"/>
       <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
-        <v>60020</v>
+        <v>60021</v>
       </c>
       <c r="B58" s="3">
         <v>6</v>
       </c>
       <c r="C58" s="8">
-        <v>5006</v>
-      </c>
-      <c r="D58" s="8">
-        <v>90000608</v>
+        <v>72003</v>
+      </c>
+      <c r="E58" s="8">
+        <v>60005</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G58" s="10">
-        <v>2</v>
-      </c>
-      <c r="H58" s="4"/>
+        <v>61</v>
+      </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="4">
-        <v>60021</v>
+        <v>60022</v>
       </c>
       <c r="B59" s="3">
         <v>6</v>
       </c>
       <c r="C59" s="8">
-        <v>72003</v>
-      </c>
-      <c r="E59" s="8">
-        <v>60005</v>
+        <v>17001</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H59" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="H59" s="3">
+        <v>100</v>
+      </c>
       <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
-        <v>60022</v>
+        <v>60023</v>
       </c>
       <c r="B60" s="3">
         <v>6</v>
       </c>
       <c r="C60" s="8">
-        <v>17001</v>
+        <v>30001</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H60" s="3">
+        <v>100</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="4">
-        <v>60023</v>
+        <v>70001</v>
       </c>
       <c r="B61" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C61" s="8">
-        <v>30001</v>
+        <v>5015</v>
+      </c>
+      <c r="D61" s="8">
+        <v>90000701</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="G61" s="3">
+        <v>2</v>
+      </c>
+      <c r="H61" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="4">
-        <v>70001</v>
+        <v>70002</v>
       </c>
       <c r="B62" s="3">
         <v>7</v>
       </c>
       <c r="C62" s="8">
-        <v>5015</v>
-      </c>
-      <c r="D62" s="8">
-        <v>90000701</v>
+        <v>55001</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="H62" s="3">
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="4">
-        <v>70002</v>
+        <v>70003</v>
       </c>
       <c r="B63" s="3">
         <v>7</v>
       </c>
       <c r="C63" s="8">
-        <v>55001</v>
+        <v>5014</v>
+      </c>
+      <c r="D63" s="8">
+        <v>90000702</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="G63" s="3">
+        <v>2</v>
+      </c>
+      <c r="H63" s="3">
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
-        <v>70003</v>
+        <v>70004</v>
       </c>
       <c r="B64" s="3">
         <v>7</v>
       </c>
       <c r="C64" s="8">
-        <v>5014</v>
+        <v>5001</v>
       </c>
       <c r="D64" s="8">
-        <v>90000702</v>
+        <v>90000703</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G64" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H64" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A65" s="4">
-        <v>70004</v>
+        <v>70005</v>
       </c>
       <c r="B65" s="3">
         <v>7</v>
       </c>
       <c r="C65" s="8">
-        <v>5001</v>
+        <v>5016</v>
       </c>
       <c r="D65" s="8">
-        <v>90000703</v>
+        <v>90000704</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G65" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="4">
-        <v>70005</v>
+        <v>70006</v>
       </c>
       <c r="B66" s="3">
         <v>7</v>
       </c>
       <c r="C66" s="8">
-        <v>5016</v>
-      </c>
-      <c r="D66" s="8">
-        <v>90000704</v>
+        <v>16001</v>
       </c>
       <c r="F66" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A67" s="4">
+        <v>70007</v>
+      </c>
+      <c r="B67" s="3">
+        <v>7</v>
+      </c>
+      <c r="C67" s="8">
+        <v>66001</v>
+      </c>
+      <c r="E67" s="8">
+        <v>70001</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G66" s="3">
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A68" s="4">
+        <v>70008</v>
+      </c>
+      <c r="B68" s="3">
+        <v>7</v>
+      </c>
+      <c r="C68" s="8">
+        <v>5019</v>
+      </c>
+      <c r="D68" s="8">
+        <v>90000705</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G68" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A67" s="4">
-        <v>70006</v>
-      </c>
-      <c r="B67" s="3">
-        <v>7</v>
-      </c>
-      <c r="C67" s="8">
-        <v>16001</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A68" s="4">
-        <v>70007</v>
-      </c>
-      <c r="B68" s="3">
-        <v>7</v>
-      </c>
-      <c r="C68" s="8">
-        <v>66001</v>
-      </c>
-      <c r="E68" s="8">
-        <v>70001</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A69" s="4">
-        <v>70008</v>
+        <v>70009</v>
       </c>
       <c r="B69" s="3">
         <v>7</v>
       </c>
       <c r="C69" s="8">
-        <v>5019</v>
-      </c>
-      <c r="D69" s="8">
-        <v>90000705</v>
+        <v>16003</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G69" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="4">
-        <v>70009</v>
+        <v>70010</v>
       </c>
       <c r="B70" s="3">
         <v>7</v>
       </c>
       <c r="C70" s="8">
-        <v>16003</v>
+        <v>72003</v>
+      </c>
+      <c r="E70" s="8">
+        <v>70002</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="4">
-        <v>70010</v>
+        <v>70011</v>
       </c>
       <c r="B71" s="3">
         <v>7</v>
       </c>
       <c r="C71" s="8">
-        <v>72003</v>
-      </c>
-      <c r="E71" s="8">
-        <v>70002</v>
+        <v>5017</v>
+      </c>
+      <c r="D71" s="8">
+        <v>90000706</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="4">
-        <v>70011</v>
+        <v>70012</v>
       </c>
       <c r="B72" s="3">
         <v>7</v>
       </c>
       <c r="C72" s="8">
-        <v>5017</v>
-      </c>
-      <c r="D72" s="8">
-        <v>90000706</v>
+        <v>20001</v>
       </c>
       <c r="F72" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A73" s="4">
+        <v>70013</v>
+      </c>
+      <c r="B73" s="3">
+        <v>7</v>
+      </c>
+      <c r="C73" s="8">
+        <v>72001</v>
+      </c>
+      <c r="E73" s="8">
+        <v>70003</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A74" s="4">
+        <v>70014</v>
+      </c>
+      <c r="B74" s="3">
+        <v>7</v>
+      </c>
+      <c r="C74" s="8">
+        <v>43001</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A75" s="4">
+        <v>70015</v>
+      </c>
+      <c r="B75" s="3">
+        <v>7</v>
+      </c>
+      <c r="C75" s="8">
+        <v>71001</v>
+      </c>
+      <c r="E75" s="8">
+        <v>70004</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A76" s="4">
+        <v>70016</v>
+      </c>
+      <c r="B76" s="3">
+        <v>7</v>
+      </c>
+      <c r="C76" s="8">
+        <v>2001</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A77" s="4">
+        <v>70017</v>
+      </c>
+      <c r="B77" s="3">
+        <v>7</v>
+      </c>
+      <c r="C77" s="8">
+        <v>5012</v>
+      </c>
+      <c r="D77" s="8">
+        <v>90000707</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2</v>
+      </c>
+      <c r="H77" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A78" s="4">
+        <v>70018</v>
+      </c>
+      <c r="B78" s="3">
+        <v>7</v>
+      </c>
+      <c r="C78" s="8">
+        <v>5011</v>
+      </c>
+      <c r="D78" s="8">
+        <v>90000708</v>
+      </c>
+      <c r="F78" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="G72" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A73" s="4">
-        <v>70012</v>
-      </c>
-      <c r="B73" s="3">
-        <v>7</v>
-      </c>
-      <c r="C73" s="8">
-        <v>20001</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A74" s="4">
-        <v>70013</v>
-      </c>
-      <c r="B74" s="3">
-        <v>7</v>
-      </c>
-      <c r="C74" s="8">
-        <v>72001</v>
-      </c>
-      <c r="E74" s="8">
-        <v>70003</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A75" s="4">
-        <v>70014</v>
-      </c>
-      <c r="B75" s="3">
-        <v>7</v>
-      </c>
-      <c r="C75" s="8">
-        <v>43001</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A76" s="4">
-        <v>70015</v>
-      </c>
-      <c r="B76" s="3">
-        <v>7</v>
-      </c>
-      <c r="C76" s="8">
-        <v>71001</v>
-      </c>
-      <c r="E76" s="8">
-        <v>70004</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A77" s="4">
-        <v>70016</v>
-      </c>
-      <c r="B77" s="3">
-        <v>7</v>
-      </c>
-      <c r="C77" s="8">
-        <v>2001</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G77" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A78" s="4">
-        <v>70017</v>
-      </c>
-      <c r="B78" s="3">
-        <v>7</v>
-      </c>
-      <c r="C78" s="8">
-        <v>5012</v>
-      </c>
-      <c r="D78" s="8">
-        <v>90000707</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="G78" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H78" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="4">
-        <v>70018</v>
+        <v>70019</v>
       </c>
       <c r="B79" s="3">
         <v>7</v>
       </c>
       <c r="C79" s="8">
-        <v>5011</v>
-      </c>
-      <c r="D79" s="8">
-        <v>90000708</v>
+        <v>6001</v>
       </c>
       <c r="F79" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A80" s="4">
+        <v>70020</v>
+      </c>
+      <c r="B80" s="3">
+        <v>7</v>
+      </c>
+      <c r="C80" s="8">
+        <v>66002</v>
+      </c>
+      <c r="E80" s="8">
+        <v>70005</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A81" s="4">
+        <v>70021</v>
+      </c>
+      <c r="B81" s="3">
+        <v>7</v>
+      </c>
+      <c r="C81" s="8">
+        <v>5013</v>
+      </c>
+      <c r="D81" s="8">
+        <v>90000709</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G81" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A80" s="4">
-        <v>70019</v>
-      </c>
-      <c r="B80" s="3">
-        <v>7</v>
-      </c>
-      <c r="C80" s="8">
-        <v>6001</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A81" s="4">
-        <v>70020</v>
-      </c>
-      <c r="B81" s="3">
-        <v>7</v>
-      </c>
-      <c r="C81" s="8">
-        <v>66002</v>
-      </c>
-      <c r="E81" s="8">
-        <v>70005</v>
-      </c>
-      <c r="F81" s="8" t="s">
+      <c r="H81" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A82" s="4">
+        <v>70022</v>
+      </c>
+      <c r="B82" s="3">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8">
+        <v>5018</v>
+      </c>
+      <c r="D82" s="8">
+        <v>90000710</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A82" s="4">
-        <v>70021</v>
-      </c>
-      <c r="B82" s="3">
-        <v>7</v>
-      </c>
-      <c r="C82" s="8">
-        <v>5013</v>
-      </c>
-      <c r="D82" s="8">
-        <v>90000709</v>
-      </c>
-      <c r="F82" s="8" t="s">
+      <c r="G82" s="3">
+        <v>3</v>
+      </c>
+      <c r="H82" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A83" s="4">
+        <v>70023</v>
+      </c>
+      <c r="B83" s="3">
+        <v>7</v>
+      </c>
+      <c r="C83" s="8">
+        <v>48001</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A84" s="4">
+        <v>70024</v>
+      </c>
+      <c r="B84" s="3">
+        <v>7</v>
+      </c>
+      <c r="C84" s="8">
+        <v>5010</v>
+      </c>
+      <c r="D84" s="8">
+        <v>90000711</v>
+      </c>
+      <c r="F84" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G82" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A83" s="4">
-        <v>70022</v>
-      </c>
-      <c r="B83" s="3">
-        <v>7</v>
-      </c>
-      <c r="C83" s="8">
-        <v>5018</v>
-      </c>
-      <c r="D83" s="8">
-        <v>90000710</v>
-      </c>
-      <c r="F83" s="8" t="s">
+      <c r="G84" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A85" s="4">
+        <v>70025</v>
+      </c>
+      <c r="B85" s="3">
+        <v>7</v>
+      </c>
+      <c r="C85" s="8">
+        <v>10001</v>
+      </c>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G83" s="3">
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A86" s="4">
+        <v>70026</v>
+      </c>
+      <c r="B86" s="3">
+        <v>7</v>
+      </c>
+      <c r="C86" s="8">
+        <v>72002</v>
+      </c>
+      <c r="E86" s="8">
+        <v>70006</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A87" s="4">
+        <v>70027</v>
+      </c>
+      <c r="B87" s="3">
+        <v>7</v>
+      </c>
+      <c r="C87" s="8">
+        <v>5008</v>
+      </c>
+      <c r="D87" s="8">
+        <v>90000712</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G87" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A84" s="4">
-        <v>70023</v>
-      </c>
-      <c r="B84" s="3">
-        <v>7</v>
-      </c>
-      <c r="C84" s="8">
-        <v>48001</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A85" s="4">
-        <v>70024</v>
-      </c>
-      <c r="B85" s="3">
-        <v>7</v>
-      </c>
-      <c r="C85" s="8">
-        <v>5010</v>
-      </c>
-      <c r="D85" s="8">
-        <v>90000711</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G85" s="3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A88" s="4">
+        <v>70028</v>
+      </c>
+      <c r="B88" s="3">
+        <v>7</v>
+      </c>
+      <c r="C88" s="8">
+        <v>72004</v>
+      </c>
+      <c r="E88" s="8">
+        <v>70007</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A89" s="4">
+        <v>70029</v>
+      </c>
+      <c r="B89" s="3">
+        <v>7</v>
+      </c>
+      <c r="C89" s="8">
+        <v>71002</v>
+      </c>
+      <c r="E89" s="8">
+        <v>70008</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A90" s="4">
+        <v>70030</v>
+      </c>
+      <c r="B90" s="3">
+        <v>7</v>
+      </c>
+      <c r="C90" s="8">
+        <v>2003</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G90" s="3">
+        <v>5</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A91" s="4">
+        <v>70031</v>
+      </c>
+      <c r="B91" s="3">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8">
+        <v>5006</v>
+      </c>
+      <c r="D91" s="8">
+        <v>90000713</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G91" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A86" s="4">
-        <v>70025</v>
-      </c>
-      <c r="B86" s="3">
-        <v>7</v>
-      </c>
-      <c r="C86" s="8">
-        <v>10001</v>
-      </c>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A87" s="4">
-        <v>70026</v>
-      </c>
-      <c r="B87" s="3">
-        <v>7</v>
-      </c>
-      <c r="C87" s="8">
-        <v>72002</v>
-      </c>
-      <c r="E87" s="8">
-        <v>70006</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A88" s="4">
-        <v>70027</v>
-      </c>
-      <c r="B88" s="3">
-        <v>7</v>
-      </c>
-      <c r="C88" s="8">
-        <v>5008</v>
-      </c>
-      <c r="D88" s="8">
-        <v>90000712</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G88" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A89" s="4">
-        <v>70028</v>
-      </c>
-      <c r="B89" s="3">
-        <v>7</v>
-      </c>
-      <c r="C89" s="8">
-        <v>72004</v>
-      </c>
-      <c r="E89" s="8">
-        <v>70007</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A90" s="4">
-        <v>70029</v>
-      </c>
-      <c r="B90" s="3">
-        <v>7</v>
-      </c>
-      <c r="C90" s="8">
-        <v>71002</v>
-      </c>
-      <c r="E90" s="8">
-        <v>70008</v>
-      </c>
-      <c r="F90" s="8" t="s">
+      <c r="H91" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A92" s="4">
+        <v>70032</v>
+      </c>
+      <c r="B92" s="3">
+        <v>7</v>
+      </c>
+      <c r="C92" s="8">
+        <v>5005</v>
+      </c>
+      <c r="D92" s="8">
+        <v>90000714</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A91" s="4">
-        <v>70030</v>
-      </c>
-      <c r="B91" s="3">
-        <v>7</v>
-      </c>
-      <c r="C91" s="8">
-        <v>2003</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G91" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A92" s="4">
-        <v>70031</v>
-      </c>
-      <c r="B92" s="3">
-        <v>7</v>
-      </c>
-      <c r="C92" s="8">
-        <v>5006</v>
-      </c>
-      <c r="D92" s="8">
-        <v>90000713</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="G92" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H92" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A93" s="4">
-        <v>70032</v>
+        <v>70033</v>
       </c>
       <c r="B93" s="3">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>5005</v>
-      </c>
-      <c r="D93" s="8">
-        <v>90000714</v>
+        <v>16005</v>
       </c>
       <c r="F93" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H93" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A94" s="4">
+        <v>70034</v>
+      </c>
+      <c r="B94" s="3">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8">
+        <v>41001</v>
+      </c>
+      <c r="F94" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G93" s="3">
+      <c r="H94" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A95" s="4">
+        <v>70035</v>
+      </c>
+      <c r="B95" s="3">
+        <v>7</v>
+      </c>
+      <c r="C95" s="8">
+        <v>66003</v>
+      </c>
+      <c r="E95" s="8">
+        <v>70009</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A96" s="4">
+        <v>70036</v>
+      </c>
+      <c r="B96" s="3">
+        <v>7</v>
+      </c>
+      <c r="C96" s="8">
+        <v>5007</v>
+      </c>
+      <c r="D96" s="8">
+        <v>90000715</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G96" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A94" s="4">
-        <v>70033</v>
-      </c>
-      <c r="B94" s="3">
-        <v>7</v>
-      </c>
-      <c r="C94" s="8">
-        <v>16005</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A95" s="4">
-        <v>70034</v>
-      </c>
-      <c r="B95" s="3">
-        <v>7</v>
-      </c>
-      <c r="C95" s="8">
-        <v>41001</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A96" s="4">
-        <v>70035</v>
-      </c>
-      <c r="B96" s="3">
-        <v>7</v>
-      </c>
-      <c r="C96" s="8">
-        <v>66003</v>
-      </c>
-      <c r="E96" s="8">
-        <v>70009</v>
-      </c>
-      <c r="F96" s="8" t="s">
+      <c r="H96" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A97" s="4">
+        <v>70037</v>
+      </c>
+      <c r="B97" s="3">
+        <v>7</v>
+      </c>
+      <c r="C97" s="8">
+        <v>66004</v>
+      </c>
+      <c r="E97" s="8">
+        <v>70011</v>
+      </c>
+      <c r="F97" s="8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A97" s="4">
-        <v>70036</v>
-      </c>
-      <c r="B97" s="3">
-        <v>7</v>
-      </c>
-      <c r="C97" s="8">
-        <v>5007</v>
-      </c>
-      <c r="D97" s="8">
-        <v>90000715</v>
-      </c>
-      <c r="F97" s="8" t="s">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A98" s="4">
+        <v>70038</v>
+      </c>
+      <c r="B98" s="3">
+        <v>7</v>
+      </c>
+      <c r="C98" s="8">
+        <v>5004</v>
+      </c>
+      <c r="D98" s="8">
+        <v>90000716</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G98" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A98" s="4">
-        <v>70037</v>
-      </c>
-      <c r="B98" s="3">
-        <v>7</v>
-      </c>
-      <c r="C98" s="8">
-        <v>66004</v>
-      </c>
-      <c r="E98" s="8">
-        <v>70011</v>
-      </c>
-      <c r="F98" s="8" t="s">
+      <c r="H98" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A99" s="4">
+        <v>70039</v>
+      </c>
+      <c r="B99" s="3">
+        <v>7</v>
+      </c>
+      <c r="C99" s="8">
+        <v>5003</v>
+      </c>
+      <c r="D99" s="8">
+        <v>90000717</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A99" s="4">
-        <v>70038</v>
-      </c>
-      <c r="B99" s="3">
-        <v>7</v>
-      </c>
-      <c r="C99" s="8">
-        <v>5004</v>
-      </c>
-      <c r="D99" s="8">
-        <v>90000716</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="G99" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H99" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A100" s="4">
-        <v>70039</v>
+        <v>70040</v>
       </c>
       <c r="B100" s="3">
         <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>5003</v>
-      </c>
-      <c r="D100" s="8">
-        <v>90000717</v>
+        <v>28001</v>
       </c>
       <c r="F100" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H100" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A101" s="4">
+        <v>70041</v>
+      </c>
+      <c r="B101" s="3">
+        <v>7</v>
+      </c>
+      <c r="C101" s="8">
+        <v>21001</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H101" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A102" s="4">
+        <v>70042</v>
+      </c>
+      <c r="B102" s="3">
+        <v>7</v>
+      </c>
+      <c r="C102" s="8">
+        <v>30001</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H102" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A103" s="4">
+        <v>70043</v>
+      </c>
+      <c r="B103" s="3">
+        <v>7</v>
+      </c>
+      <c r="C103" s="8">
+        <v>5009</v>
+      </c>
+      <c r="D103" s="8">
+        <v>90000718</v>
+      </c>
+      <c r="F103" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G103" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A101" s="4">
-        <v>70040</v>
-      </c>
-      <c r="B101" s="3">
-        <v>7</v>
-      </c>
-      <c r="C101" s="8">
-        <v>28001</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A102" s="4">
-        <v>70041</v>
-      </c>
-      <c r="B102" s="3">
-        <v>7</v>
-      </c>
-      <c r="C102" s="8">
-        <v>21001</v>
-      </c>
-      <c r="F102" s="8" t="s">
+      <c r="H103" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A104" s="4">
+        <v>70044</v>
+      </c>
+      <c r="B104" s="3">
+        <v>7</v>
+      </c>
+      <c r="C104" s="8">
+        <v>9001</v>
+      </c>
+      <c r="F104" s="8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A103" s="4">
-        <v>70042</v>
-      </c>
-      <c r="B103" s="3">
-        <v>7</v>
-      </c>
-      <c r="C103" s="8">
-        <v>30001</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A104" s="4">
-        <v>70043</v>
-      </c>
-      <c r="B104" s="3">
-        <v>7</v>
-      </c>
-      <c r="C104" s="8">
-        <v>5009</v>
-      </c>
-      <c r="D104" s="8">
-        <v>90000718</v>
-      </c>
-      <c r="F104" s="8" t="s">
+      <c r="H104" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A105" s="4">
+        <v>70045</v>
+      </c>
+      <c r="B105" s="3">
+        <v>7</v>
+      </c>
+      <c r="C105" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D105" s="8">
+        <v>90000719</v>
+      </c>
+      <c r="F105" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G105" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A105" s="4">
-        <v>70044</v>
-      </c>
-      <c r="B105" s="3">
-        <v>7</v>
-      </c>
-      <c r="C105" s="8">
-        <v>9001</v>
-      </c>
-      <c r="F105" s="8" t="s">
+      <c r="H105" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A106" s="4">
+        <v>70046</v>
+      </c>
+      <c r="B106" s="3">
+        <v>7</v>
+      </c>
+      <c r="C106" s="8">
+        <v>72005</v>
+      </c>
+      <c r="E106" s="8">
+        <v>70012</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A106" s="4">
-        <v>70045</v>
-      </c>
-      <c r="B106" s="3">
-        <v>7</v>
-      </c>
-      <c r="C106" s="8">
-        <v>5002</v>
-      </c>
-      <c r="D106" s="8">
-        <v>90000719</v>
-      </c>
-      <c r="F106" s="8" t="s">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A107" s="4">
+        <v>70047</v>
+      </c>
+      <c r="B107" s="3">
+        <v>7</v>
+      </c>
+      <c r="C107" s="8">
+        <v>17001</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A108" s="4">
+        <v>70048</v>
+      </c>
+      <c r="B108" s="3">
+        <v>7</v>
+      </c>
+      <c r="C108" s="8">
+        <v>71003</v>
+      </c>
+      <c r="E108" s="8">
+        <v>70013</v>
+      </c>
+      <c r="F108" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="G106" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A107" s="4">
-        <v>70046</v>
-      </c>
-      <c r="B107" s="3">
-        <v>7</v>
-      </c>
-      <c r="C107" s="8">
-        <v>72005</v>
-      </c>
-      <c r="E107" s="8">
-        <v>70012</v>
-      </c>
-      <c r="F107" s="8" t="s">
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A109" s="4">
+        <v>70049</v>
+      </c>
+      <c r="B109" s="3">
+        <v>7</v>
+      </c>
+      <c r="C109" s="8">
+        <v>2009</v>
+      </c>
+      <c r="F109" s="10" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A108" s="4">
-        <v>70047</v>
-      </c>
-      <c r="B108" s="3">
-        <v>7</v>
-      </c>
-      <c r="C108" s="8">
-        <v>17001</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A109" s="4">
-        <v>70048</v>
-      </c>
-      <c r="B109" s="3">
-        <v>7</v>
-      </c>
-      <c r="C109" s="8">
-        <v>71003</v>
-      </c>
-      <c r="E109" s="8">
-        <v>70013</v>
-      </c>
-      <c r="F109" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A110" s="4">
-        <v>70049</v>
-      </c>
-      <c r="B110" s="3">
-        <v>7</v>
-      </c>
-      <c r="C110" s="8">
-        <v>2009</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G110" s="3">
+      <c r="G109" s="3">
         <v>6</v>
+      </c>
+      <c r="I109" s="11">
+        <v>50100</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8CBDC6-75A6-4567-B184-813E3917AAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A752712-7CA7-4AC8-AD8E-A0FA31AA2686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1704,7 +1704,7 @@
         <v>46</v>
       </c>
       <c r="H37" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I37" s="4"/>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A752712-7CA7-4AC8-AD8E-A0FA31AA2686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3CBDD9-E7DB-455F-9D9D-4F26BB487C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1317,7 +1317,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="8">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="D18" s="8">
         <v>90000302</v>
@@ -1920,7 +1920,7 @@
         <v>6</v>
       </c>
       <c r="C48" s="8">
-        <v>16002</v>
+        <v>16001</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>38</v>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3CBDD9-E7DB-455F-9D9D-4F26BB487C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1619458-92F3-413E-94E8-917886A1690E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="101">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -359,6 +359,10 @@
   </si>
   <si>
     <t>20,10,60,20,120,30,200,40,300,60,420,80,560,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -488,7 +492,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1450,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="8">
-        <v>160001</v>
+        <v>16001</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>38</v>
@@ -3094,8 +3098,8 @@
       <c r="G109" s="3">
         <v>6</v>
       </c>
-      <c r="I109" s="11">
-        <v>50100</v>
+      <c r="I109" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1619458-92F3-413E-94E8-917886A1690E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B0442E-1F48-431D-A27A-80259187A72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="103">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -107,10 +107,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>刷怪增加砝码值（刷怪进度，增加砝码值；两个数为一组数据）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>STRING</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -350,19 +346,31 @@
     <t>刷怪区域3</t>
   </si>
   <si>
-    <t>10,10,30,20,60,30,100,40,150,60,210,80,300,100</t>
+    <t>刷怪增加砝码值（刷怪进度，增加砝码值，猪妖后退距离；三个数为一组数据）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>10,20,30,40,60,60,100,80,150,120,210,160,300,200</t>
+    <t>add_save_item</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>20,10,60,20,120,30,200,40,300,60,420,80,560,100</t>
+    <t>save_item_pos</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>50,100</t>
+    <t>掉落道具位置（万分比）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加道具id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,20,2000,30,40,3000,60,60,3500,100,80,4000,150,120,4500,210,160,5000,300,200,5000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,100,3000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -901,7 +909,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -912,11 +920,13 @@
     <col min="6" max="6" width="21.625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="58.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="92.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -927,16 +937,18 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -945,19 +957,25 @@
         <v>4</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="K2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -974,7 +992,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -985,8 +1003,14 @@
       <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="J3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1003,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -1012,10 +1036,16 @@
         <v>16</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+        <v>96</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1029,19 +1059,16 @@
         <v>90000101</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
       </c>
-      <c r="H5" s="3">
-        <v>100</v>
-      </c>
       <c r="I5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1053,17 +1080,20 @@
       </c>
       <c r="D6" s="8"/>
       <c r="F6" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="8"/>
-      <c r="H6" s="3">
-        <v>100</v>
-      </c>
       <c r="I6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1075,16 +1105,16 @@
       </c>
       <c r="D7" s="8"/>
       <c r="F7" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="8">
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1098,19 +1128,16 @@
         <v>90000102</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
       </c>
-      <c r="H8" s="3">
-        <v>100</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>20001</v>
       </c>
@@ -1124,19 +1151,16 @@
         <v>90000201</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="3">
-        <v>100</v>
-      </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>20002</v>
       </c>
@@ -1147,17 +1171,20 @@
         <v>16001</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="8"/>
-      <c r="H10" s="3">
-        <v>50</v>
-      </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J10" s="3">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>20003</v>
       </c>
@@ -1168,16 +1195,16 @@
         <v>2001</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" s="8">
         <v>2</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>20004</v>
       </c>
@@ -1192,19 +1219,16 @@
       </c>
       <c r="E12"/>
       <c r="F12" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="8">
         <v>1</v>
       </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
       <c r="I12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>20005</v>
       </c>
@@ -1215,17 +1239,14 @@
         <v>6001</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="8"/>
-      <c r="H13" s="3">
-        <v>50</v>
-      </c>
       <c r="I13" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>20006</v>
       </c>
@@ -1236,16 +1257,13 @@
         <v>17001</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="3">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>30001</v>
       </c>
@@ -1259,19 +1277,16 @@
         <v>90000301</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>
       </c>
-      <c r="H15" s="3">
-        <v>100</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>30002</v>
       </c>
@@ -1283,10 +1298,7 @@
       </c>
       <c r="D16" s="8"/>
       <c r="F16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="3">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="I16" s="3">
         <v>0</v>
@@ -1304,13 +1316,13 @@
       </c>
       <c r="D17" s="8"/>
       <c r="F17" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17" s="3">
         <v>3</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
@@ -1327,13 +1339,10 @@
         <v>90000302</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
-      </c>
-      <c r="H18" s="3">
-        <v>100</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -1351,10 +1360,7 @@
       </c>
       <c r="D19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="3">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="I19" s="3">
         <v>0</v>
@@ -1374,13 +1380,10 @@
         <v>90000400</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -1395,10 +1398,7 @@
         <v>6001</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -1413,13 +1413,13 @@
         <v>2001</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3">
         <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
@@ -1436,13 +1436,10 @@
         <v>90000401</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="3">
         <v>1</v>
-      </c>
-      <c r="H23" s="3">
-        <v>100</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -1457,10 +1454,7 @@
         <v>16001</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -1478,7 +1472,7 @@
         <v>90000402</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G25" s="3">
         <v>1</v>
@@ -1499,7 +1493,7 @@
         <v>40001</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I26" s="4"/>
     </row>
@@ -1514,10 +1508,7 @@
         <v>20001</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="3">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="I27" s="4"/>
     </row>
@@ -1535,13 +1526,10 @@
         <v>90000502</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
-      </c>
-      <c r="H28" s="3">
-        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.15">
@@ -1555,10 +1543,7 @@
         <v>20001</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="3">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
@@ -1572,10 +1557,7 @@
         <v>28001</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H30" s="3">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.15">
@@ -1589,13 +1571,13 @@
         <v>2001</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G31" s="3">
         <v>3</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.15">
@@ -1612,13 +1594,10 @@
         <v>90000503</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G32" s="3">
         <v>2</v>
-      </c>
-      <c r="H32" s="3">
-        <v>100</v>
       </c>
       <c r="I32" s="4"/>
     </row>
@@ -1636,7 +1615,7 @@
         <v>90000504</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G33" s="3">
         <v>2</v>
@@ -1654,7 +1633,7 @@
         <v>6001</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I34" s="4"/>
     </row>
@@ -1672,7 +1651,7 @@
         <v>50001</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I35" s="4"/>
     </row>
@@ -1687,10 +1666,7 @@
         <v>16001</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="3">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="I36" s="4"/>
     </row>
@@ -1705,10 +1681,7 @@
         <v>16003</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H37" s="3">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="I37" s="4"/>
     </row>
@@ -1726,13 +1699,10 @@
         <v>90000601</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G38" s="3">
         <v>2</v>
-      </c>
-      <c r="H38" s="3">
-        <v>50</v>
       </c>
       <c r="I38" s="4"/>
     </row>
@@ -1751,7 +1721,7 @@
         <v>60001</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I39" s="4"/>
     </row>
@@ -1769,13 +1739,10 @@
         <v>90000602</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G40" s="3">
         <v>2</v>
-      </c>
-      <c r="H40" s="3">
-        <v>50</v>
       </c>
       <c r="I40" s="4"/>
     </row>
@@ -1790,10 +1757,7 @@
         <v>48001</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H41" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I41" s="4"/>
     </row>
@@ -1808,13 +1772,13 @@
         <v>2001</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G42" s="3">
         <v>3</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.15">
@@ -1831,13 +1795,10 @@
         <v>90000603</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G43" s="3">
         <v>2</v>
-      </c>
-      <c r="H43" s="3">
-        <v>50</v>
       </c>
       <c r="I43" s="4"/>
     </row>
@@ -1852,7 +1813,7 @@
         <v>54001</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I44" s="4"/>
     </row>
@@ -1870,7 +1831,7 @@
         <v>60002</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I45" s="4"/>
     </row>
@@ -1888,13 +1849,10 @@
         <v>90000604</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G46" s="3">
         <v>2</v>
-      </c>
-      <c r="H46" s="3">
-        <v>50</v>
       </c>
       <c r="I46" s="4"/>
     </row>
@@ -1909,10 +1867,7 @@
         <v>20001</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H47" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I47" s="4"/>
     </row>
@@ -1927,10 +1882,7 @@
         <v>16001</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H48" s="3">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I48" s="4"/>
     </row>
@@ -1948,13 +1900,10 @@
         <v>90000605</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G49" s="3">
         <v>2</v>
-      </c>
-      <c r="H49" s="3">
-        <v>50</v>
       </c>
       <c r="I49" s="4"/>
     </row>
@@ -1969,10 +1918,7 @@
         <v>43001</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H50" s="3">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I50" s="4"/>
     </row>
@@ -1987,13 +1933,13 @@
         <v>2003</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G51" s="3">
         <v>4</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.15">
@@ -2010,7 +1956,7 @@
         <v>60003</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I52" s="4"/>
     </row>
@@ -2028,13 +1974,10 @@
         <v>90000606</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G53" s="3">
         <v>2</v>
-      </c>
-      <c r="H53" s="3">
-        <v>50</v>
       </c>
       <c r="I53" s="4"/>
     </row>
@@ -2049,10 +1992,7 @@
         <v>16003</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H54" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I54" s="4"/>
     </row>
@@ -2070,7 +2010,7 @@
         <v>60004</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I55" s="4"/>
     </row>
@@ -2088,13 +2028,10 @@
         <v>90000607</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G56" s="3">
         <v>2</v>
-      </c>
-      <c r="H56" s="3">
-        <v>50</v>
       </c>
       <c r="I56" s="4"/>
     </row>
@@ -2112,7 +2049,7 @@
         <v>90000608</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G57" s="3">
         <v>2</v>
@@ -2133,7 +2070,7 @@
         <v>60005</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I58" s="4"/>
     </row>
@@ -2148,10 +2085,7 @@
         <v>17001</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I59" s="4"/>
     </row>
@@ -2166,10 +2100,7 @@
         <v>30001</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H60" s="3">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.15">
@@ -2186,13 +2117,10 @@
         <v>90000701</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G61" s="3">
         <v>2</v>
-      </c>
-      <c r="H61" s="3">
-        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.15">
@@ -2206,10 +2134,7 @@
         <v>55001</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H62" s="3">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.15">
@@ -2226,13 +2151,10 @@
         <v>90000702</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G63" s="3">
         <v>2</v>
-      </c>
-      <c r="H63" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.15">
@@ -2249,13 +2171,10 @@
         <v>90000703</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G64" s="3">
         <v>2</v>
-      </c>
-      <c r="H64" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.15">
@@ -2272,7 +2191,7 @@
         <v>90000704</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G65" s="3">
         <v>2</v>
@@ -2289,7 +2208,7 @@
         <v>16001</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.15">
@@ -2306,7 +2225,7 @@
         <v>70001</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.15">
@@ -2323,7 +2242,7 @@
         <v>90000705</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G68" s="3">
         <v>2</v>
@@ -2340,7 +2259,7 @@
         <v>16003</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.15">
@@ -2357,7 +2276,7 @@
         <v>70002</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.15">
@@ -2374,7 +2293,7 @@
         <v>90000706</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G71" s="3">
         <v>2</v>
@@ -2391,7 +2310,7 @@
         <v>20001</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.15">
@@ -2408,7 +2327,7 @@
         <v>70003</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.15">
@@ -2422,10 +2341,7 @@
         <v>43001</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H74" s="3">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.15">
@@ -2442,7 +2358,7 @@
         <v>70004</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.15">
@@ -2456,13 +2372,13 @@
         <v>2001</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G76" s="3">
         <v>4</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.15">
@@ -2479,13 +2395,10 @@
         <v>90000707</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G77" s="3">
         <v>2</v>
-      </c>
-      <c r="H77" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.15">
@@ -2502,13 +2415,10 @@
         <v>90000708</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G78" s="3">
         <v>2</v>
-      </c>
-      <c r="H78" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.15">
@@ -2522,10 +2432,7 @@
         <v>6001</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H79" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.15">
@@ -2542,7 +2449,7 @@
         <v>70005</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.15">
@@ -2559,13 +2466,10 @@
         <v>90000709</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G81" s="3">
         <v>2</v>
-      </c>
-      <c r="H81" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.15">
@@ -2582,13 +2486,10 @@
         <v>90000710</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G82" s="3">
         <v>3</v>
-      </c>
-      <c r="H82" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.15">
@@ -2602,10 +2503,7 @@
         <v>48001</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H83" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.15">
@@ -2622,7 +2520,7 @@
         <v>90000711</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G84" s="3">
         <v>3</v>
@@ -2640,7 +2538,7 @@
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.15">
@@ -2657,7 +2555,7 @@
         <v>70006</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.15">
@@ -2674,7 +2572,7 @@
         <v>90000712</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G87" s="3">
         <v>3</v>
@@ -2694,7 +2592,7 @@
         <v>70007</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.15">
@@ -2711,7 +2609,7 @@
         <v>70008</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.15">
@@ -2725,13 +2623,13 @@
         <v>2003</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G90" s="3">
         <v>5</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.15">
@@ -2748,13 +2646,10 @@
         <v>90000713</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G91" s="3">
         <v>3</v>
-      </c>
-      <c r="H91" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.15">
@@ -2771,13 +2666,10 @@
         <v>90000714</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G92" s="3">
         <v>3</v>
-      </c>
-      <c r="H92" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.15">
@@ -2791,10 +2683,7 @@
         <v>16005</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="H93" s="3">
-        <v>50</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.15">
@@ -2808,10 +2697,7 @@
         <v>41001</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H94" s="3">
-        <v>50</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.15">
@@ -2828,7 +2714,7 @@
         <v>70009</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.15">
@@ -2845,13 +2731,10 @@
         <v>90000715</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G96" s="3">
         <v>3</v>
-      </c>
-      <c r="H96" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.15">
@@ -2868,7 +2751,7 @@
         <v>70011</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.15">
@@ -2885,13 +2768,10 @@
         <v>90000716</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G98" s="3">
         <v>3</v>
-      </c>
-      <c r="H98" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.15">
@@ -2908,13 +2788,10 @@
         <v>90000717</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G99" s="3">
         <v>3</v>
-      </c>
-      <c r="H99" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.15">
@@ -2928,10 +2805,7 @@
         <v>28001</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H100" s="3">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.15">
@@ -2945,10 +2819,7 @@
         <v>21001</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H101" s="3">
-        <v>50</v>
+        <v>89</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.15">
@@ -2962,10 +2833,7 @@
         <v>30001</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H102" s="3">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.15">
@@ -2982,13 +2850,10 @@
         <v>90000718</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G103" s="3">
         <v>3</v>
-      </c>
-      <c r="H103" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.15">
@@ -3002,10 +2867,7 @@
         <v>9001</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H104" s="3">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.15">
@@ -3022,13 +2884,10 @@
         <v>90000719</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G105" s="3">
         <v>3</v>
-      </c>
-      <c r="H105" s="3">
-        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.15">
@@ -3045,7 +2904,7 @@
         <v>70012</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.15">
@@ -3059,10 +2918,7 @@
         <v>17001</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H107" s="3">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.15">
@@ -3079,7 +2935,7 @@
         <v>70013</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.15">
@@ -3093,13 +2949,13 @@
         <v>2009</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G109" s="3">
         <v>6</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B0442E-1F48-431D-A27A-80259187A72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4DD2D1-B570-4712-A457-1AEA7DE181D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -366,12 +366,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>10,20,2000,30,40,3000,60,60,3500,100,80,4000,150,120,4500,210,160,5000,300,200,5000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>50,100,3000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>10,50,2500,30,100,3000,60,150,3500,100,200,4000,150,250,4500,220,350,5000,330,500,10000</t>
   </si>
 </sst>
 </file>
@@ -920,7 +915,7 @@
     <col min="6" max="6" width="21.625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="92.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.875" style="2" customWidth="1"/>
     <col min="10" max="10" width="15" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.5" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
@@ -1087,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="3">
         <v>4000</v>
@@ -1181,7 +1176,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="3">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
@@ -1303,8 +1298,14 @@
       <c r="I16" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J16" s="3">
+        <v>2</v>
+      </c>
+      <c r="K16" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>30003</v>
       </c>
@@ -1325,7 +1326,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>30004</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>30005</v>
       </c>
@@ -1366,7 +1367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>40001</v>
       </c>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>40002</v>
       </c>
@@ -1401,8 +1402,14 @@
         <v>30</v>
       </c>
       <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J21" s="3">
+        <v>2</v>
+      </c>
+      <c r="K21" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>40003</v>
       </c>
@@ -1422,7 +1429,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>40004</v>
       </c>
@@ -1443,7 +1450,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>40005</v>
       </c>
@@ -1458,7 +1465,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>40006</v>
       </c>
@@ -1479,7 +1486,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>40007</v>
       </c>
@@ -1497,7 +1504,7 @@
       </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>40008</v>
       </c>
@@ -1512,7 +1519,7 @@
       </c>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>50001</v>
       </c>
@@ -1532,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
         <v>50002</v>
       </c>
@@ -1545,8 +1552,14 @@
       <c r="F29" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J29" s="3">
+        <v>2</v>
+      </c>
+      <c r="K29" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
         <v>50003</v>
       </c>
@@ -1559,8 +1572,14 @@
       <c r="F30" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J30" s="3">
+        <v>2</v>
+      </c>
+      <c r="K30" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>50004</v>
       </c>
@@ -1580,7 +1599,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>50005</v>
       </c>
@@ -1938,9 +1957,7 @@
       <c r="G51" s="3">
         <v>4</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
@@ -2628,9 +2645,7 @@
       <c r="G90" s="3">
         <v>5</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="I90" s="3"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A91" s="4">
@@ -2954,9 +2969,7 @@
       <c r="G109" s="3">
         <v>6</v>
       </c>
-      <c r="I109" s="11" t="s">
-        <v>102</v>
-      </c>
+      <c r="I109" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4DD2D1-B570-4712-A457-1AEA7DE181D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C977944-B8F1-4158-AFC0-38209CC20A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="3">
         <v>4000</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="3">
         <v>4000</v>
@@ -1553,7 +1553,7 @@
         <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="3">
         <v>3000</v>
@@ -1573,7 +1573,7 @@
         <v>33</v>
       </c>
       <c r="J30" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="3">
         <v>6000</v>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C977944-B8F1-4158-AFC0-38209CC20A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9BB2F0-1086-40CE-A3D1-72B9DC2A12B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="108">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -367,6 +367,28 @@
   </si>
   <si>
     <t>10,50,2500,30,100,3000,60,150,3500,100,200,4000,150,250,4500,220,350,5000,330,500,10000</t>
+  </si>
+  <si>
+    <t>6,30,900,14,60,1000,24,90,1100,36,120,1200,50,150,1300,66,180,1400,84,210,1500,104,240,1600,126,270,1700,150,300,1800,176,330,1900,204,360,2000,234,390,2100,264,420,2200,296,450,2300,330,500,10000</t>
+  </si>
+  <si>
+    <t>brush_monsters_id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷怪组id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷怪增加道具（刷怪进度，增加道具id，掉落道具位置；三个数为一组数据）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>kill_mons_add_save_items</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,5,-1,14,1,3000,24,5,-1,36,2,5000,50,5,-1,66,3,7000,84,6,-1,104,6,-1,126,6,-1,150,6,-1,176,6,-1,204,6,-1,234,6,-1,264,6,-1,296,6,-1,330,6,-1</t>
   </si>
 </sst>
 </file>
@@ -904,7 +926,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -918,10 +940,12 @@
     <col min="9" max="9" width="15.875" style="2" customWidth="1"/>
     <col min="10" max="10" width="15" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="12" max="12" width="19.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="73.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -934,8 +958,10 @@
       <c r="H1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -969,8 +995,14 @@
       <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="L2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1004,8 +1036,14 @@
       <c r="K3" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="L3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1039,8 +1077,14 @@
       <c r="K4" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="L4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1063,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1088,7 +1132,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1106,10 +1150,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1132,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>20001</v>
       </c>
@@ -1155,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>20002</v>
       </c>
@@ -1179,7 +1223,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>20003</v>
       </c>
@@ -1199,7 +1243,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>20004</v>
       </c>
@@ -1223,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>20005</v>
       </c>
@@ -1241,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>20006</v>
       </c>
@@ -1258,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>30001</v>
       </c>
@@ -1281,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>30002</v>
       </c>
@@ -1620,7 +1664,7 @@
       </c>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A33" s="4">
         <v>50006</v>
       </c>
@@ -1641,7 +1685,7 @@
       </c>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A34" s="4">
         <v>50007</v>
       </c>
@@ -1656,7 +1700,7 @@
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>50008</v>
       </c>
@@ -1674,7 +1718,7 @@
       </c>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>50009</v>
       </c>
@@ -1689,7 +1733,7 @@
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>50010</v>
       </c>
@@ -1704,7 +1748,7 @@
       </c>
       <c r="I37" s="4"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>60001</v>
       </c>
@@ -1725,7 +1769,7 @@
       </c>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>60002</v>
       </c>
@@ -1744,7 +1788,7 @@
       </c>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>60003</v>
       </c>
@@ -1765,7 +1809,7 @@
       </c>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>60004</v>
       </c>
@@ -1779,8 +1823,14 @@
         <v>49</v>
       </c>
       <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J41" s="3">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>60005</v>
       </c>
@@ -1796,11 +1846,15 @@
       <c r="G42" s="3">
         <v>3</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I42" s="3"/>
+      <c r="L42" s="3">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43" s="4">
         <v>60006</v>
       </c>
@@ -1821,7 +1875,7 @@
       </c>
       <c r="I43" s="4"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
         <v>60007</v>
       </c>
@@ -1836,7 +1890,7 @@
       </c>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45" s="4">
         <v>60008</v>
       </c>
@@ -1854,7 +1908,7 @@
       </c>
       <c r="I45" s="4"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46" s="4">
         <v>60009</v>
       </c>
@@ -1875,7 +1929,7 @@
       </c>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47" s="4">
         <v>60010</v>
       </c>
@@ -1889,8 +1943,14 @@
         <v>40</v>
       </c>
       <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J47" s="3">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
         <v>60011</v>
       </c>
@@ -1904,8 +1964,14 @@
         <v>37</v>
       </c>
       <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J48" s="3">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
         <v>60012</v>
       </c>
@@ -1926,7 +1992,7 @@
       </c>
       <c r="I49" s="4"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50" s="4">
         <v>60013</v>
       </c>
@@ -1940,8 +2006,14 @@
         <v>22</v>
       </c>
       <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J50" s="3">
+        <v>6</v>
+      </c>
+      <c r="K50" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
         <v>60014</v>
       </c>
@@ -1958,8 +2030,14 @@
         <v>4</v>
       </c>
       <c r="I51" s="3"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="L51" s="3">
+        <v>2</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
         <v>60015</v>
       </c>
@@ -1977,7 +2055,7 @@
       </c>
       <c r="I52" s="4"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A53" s="4">
         <v>60016</v>
       </c>
@@ -1998,7 +2076,7 @@
       </c>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A54" s="4">
         <v>60017</v>
       </c>
@@ -2013,7 +2091,7 @@
       </c>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A55" s="4">
         <v>60018</v>
       </c>
@@ -2031,7 +2109,7 @@
       </c>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
         <v>60019</v>
       </c>
@@ -2052,7 +2130,7 @@
       </c>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A57" s="4">
         <v>60020</v>
       </c>
@@ -2073,7 +2151,7 @@
       </c>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
         <v>60021</v>
       </c>
@@ -2091,7 +2169,7 @@
       </c>
       <c r="I58" s="4"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59" s="4">
         <v>60022</v>
       </c>
@@ -2106,7 +2184,7 @@
       </c>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
         <v>60023</v>
       </c>
@@ -2120,7 +2198,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61" s="4">
         <v>70001</v>
       </c>
@@ -2140,7 +2218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62" s="4">
         <v>70002</v>
       </c>
@@ -2154,7 +2232,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63" s="4">
         <v>70003</v>
       </c>
@@ -2174,7 +2252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
         <v>70004</v>
       </c>
@@ -2194,7 +2272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65" s="4">
         <v>70005</v>
       </c>
@@ -2214,7 +2292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66" s="4">
         <v>70006</v>
       </c>
@@ -2228,7 +2306,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67" s="4">
         <v>70007</v>
       </c>
@@ -2245,7 +2323,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68" s="4">
         <v>70008</v>
       </c>
@@ -2265,7 +2343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69" s="4">
         <v>70009</v>
       </c>
@@ -2279,7 +2357,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70" s="4">
         <v>70010</v>
       </c>
@@ -2296,7 +2374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71" s="4">
         <v>70011</v>
       </c>
@@ -2316,7 +2394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72" s="4">
         <v>70012</v>
       </c>
@@ -2330,7 +2408,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73" s="4">
         <v>70013</v>
       </c>
@@ -2347,7 +2425,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74" s="4">
         <v>70014</v>
       </c>
@@ -2361,7 +2439,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75" s="4">
         <v>70015</v>
       </c>
@@ -2378,7 +2456,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76" s="4">
         <v>70016</v>
       </c>
@@ -2394,11 +2472,15 @@
       <c r="G76" s="3">
         <v>4</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I76" s="3"/>
+      <c r="L76" s="3">
+        <v>1</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A77" s="4">
         <v>70017</v>
       </c>
@@ -2418,7 +2500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A78" s="4">
         <v>70018</v>
       </c>
@@ -2438,7 +2520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79" s="4">
         <v>70019</v>
       </c>
@@ -2452,7 +2534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80" s="4">
         <v>70020</v>
       </c>
@@ -2469,7 +2551,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A81" s="4">
         <v>70021</v>
       </c>
@@ -2489,7 +2571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A82" s="4">
         <v>70022</v>
       </c>
@@ -2509,7 +2591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A83" s="4">
         <v>70023</v>
       </c>
@@ -2523,7 +2605,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84" s="4">
         <v>70024</v>
       </c>
@@ -2543,7 +2625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A85" s="4">
         <v>70025</v>
       </c>
@@ -2558,7 +2640,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A86" s="4">
         <v>70026</v>
       </c>
@@ -2575,7 +2657,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A87" s="4">
         <v>70027</v>
       </c>
@@ -2595,7 +2677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A88" s="4">
         <v>70028</v>
       </c>
@@ -2612,7 +2694,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A89" s="4">
         <v>70029</v>
       </c>
@@ -2629,7 +2711,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A90" s="4">
         <v>70030</v>
       </c>
@@ -2646,8 +2728,14 @@
         <v>5</v>
       </c>
       <c r="I90" s="3"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="L90" s="3">
+        <v>2</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A91" s="4">
         <v>70031</v>
       </c>
@@ -2667,7 +2755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A92" s="4">
         <v>70032</v>
       </c>
@@ -2687,7 +2775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A93" s="4">
         <v>70033</v>
       </c>
@@ -2701,7 +2789,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A94" s="4">
         <v>70034</v>
       </c>
@@ -2715,7 +2803,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A95" s="4">
         <v>70035</v>
       </c>
@@ -2732,7 +2820,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A96" s="4">
         <v>70036</v>
       </c>
@@ -2752,7 +2840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A97" s="4">
         <v>70037</v>
       </c>
@@ -2769,7 +2857,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A98" s="4">
         <v>70038</v>
       </c>
@@ -2789,7 +2877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A99" s="4">
         <v>70039</v>
       </c>
@@ -2809,7 +2897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A100" s="4">
         <v>70040</v>
       </c>
@@ -2823,7 +2911,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="4">
         <v>70041</v>
       </c>
@@ -2837,7 +2925,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A102" s="4">
         <v>70042</v>
       </c>
@@ -2851,7 +2939,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A103" s="4">
         <v>70043</v>
       </c>
@@ -2871,7 +2959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A104" s="4">
         <v>70044</v>
       </c>
@@ -2885,7 +2973,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A105" s="4">
         <v>70045</v>
       </c>
@@ -2905,7 +2993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A106" s="4">
         <v>70046</v>
       </c>
@@ -2922,7 +3010,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A107" s="4">
         <v>70047</v>
       </c>
@@ -2936,7 +3024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A108" s="4">
         <v>70048</v>
       </c>
@@ -2953,7 +3041,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A109" s="4">
         <v>70049</v>
       </c>
@@ -2970,6 +3058,9 @@
         <v>6</v>
       </c>
       <c r="I109" s="11"/>
+      <c r="L109" s="3">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9BB2F0-1086-40CE-A3D1-72B9DC2A12B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47156363-F104-464A-99E1-57ACA3E00EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_map_editor_config_id_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -366,12 +366,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>10,50,2500,30,100,3000,60,150,3500,100,200,4000,150,250,4500,220,350,5000,330,500,10000</t>
-  </si>
-  <si>
-    <t>6,30,900,14,60,1000,24,90,1100,36,120,1200,50,150,1300,66,180,1400,84,210,1500,104,240,1600,126,270,1700,150,300,1800,176,330,1900,204,360,2000,234,390,2100,264,420,2200,296,450,2300,330,500,10000</t>
-  </si>
-  <si>
     <t>brush_monsters_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -389,6 +383,9 @@
   </si>
   <si>
     <t>6,5,-1,14,1,3000,24,5,-1,36,2,5000,50,5,-1,66,3,7000,84,6,-1,104,6,-1,126,6,-1,150,6,-1,176,6,-1,204,6,-1,234,6,-1,264,6,-1,296,6,-1,330,6,-1</t>
+  </si>
+  <si>
+    <t>6,30,1800,14,60,1800,24,90,1750,36,120,1750,50,150,1700,66,180,1700,84,210,1650,104,240,1650,126,270,1600,150,300,1600,176,330,1550,204,360,1550,234,390,1500,264,420,1500,296,450,1450,330,500,10000</t>
   </si>
 </sst>
 </file>
@@ -1037,10 +1034,10 @@
         <v>98</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -1078,10 +1075,10 @@
         <v>99</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.15">
@@ -1150,7 +1147,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
@@ -1240,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
@@ -1367,7 +1364,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
@@ -1470,7 +1467,7 @@
         <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
@@ -1640,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
@@ -1851,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.15">
@@ -2034,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.15">
@@ -2477,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.15">
@@ -2732,7 +2729,7 @@
         <v>2</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47156363-F104-464A-99E1-57ACA3E00EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DFDFE0-1D20-4AA8-97FF-B04B4EBA15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_map_editor_config_id_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="109">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -386,6 +386,12 @@
   </si>
   <si>
     <t>6,30,1800,14,60,1800,24,90,1750,36,120,1750,50,150,1700,66,180,1700,84,210,1650,104,240,1650,126,270,1600,150,300,1600,176,330,1550,204,360,1550,234,390,1500,264,420,1500,296,450,1450,330,500,10000</t>
+  </si>
+  <si>
+    <t>6,5,-1,14,1,3000,24,5,-1,36,6,-1,50,5,-1,66,2,4500,84,5,-1,104,5,-1,126,6,-1,150,3,6500,176,5,-1,204,6,-1,234,3,8500,270,5,-1,310,6,-1</t>
+  </si>
+  <si>
+    <t>5,5,-1,12,6,-1,18,6,-1</t>
   </si>
 </sst>
 </file>
@@ -1123,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="3">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
@@ -1217,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="3">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
@@ -1340,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="3">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
@@ -1447,7 +1453,7 @@
         <v>2</v>
       </c>
       <c r="K21" s="3">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
@@ -1597,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
@@ -1617,7 +1623,7 @@
         <v>3</v>
       </c>
       <c r="K30" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
@@ -1848,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.15">
@@ -1961,12 +1967,6 @@
         <v>37</v>
       </c>
       <c r="I48" s="4"/>
-      <c r="J48" s="3">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
-        <v>-1</v>
-      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" s="3">
         <v>-1</v>
@@ -2435,6 +2435,12 @@
       <c r="F74" s="8" t="s">
         <v>22</v>
       </c>
+      <c r="J74" s="3">
+        <v>5</v>
+      </c>
+      <c r="K74" s="3">
+        <v>-1</v>
+      </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75" s="4">
@@ -2474,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.15">
@@ -2530,6 +2536,12 @@
       <c r="F79" s="8" t="s">
         <v>30</v>
       </c>
+      <c r="J79" s="3">
+        <v>4</v>
+      </c>
+      <c r="K79" s="3">
+        <v>4000</v>
+      </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80" s="4">
@@ -2601,6 +2613,12 @@
       <c r="F83" s="8" t="s">
         <v>49</v>
       </c>
+      <c r="J83" s="3">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
+        <v>-1</v>
+      </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84" s="4">
@@ -2837,7 +2855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A97" s="4">
         <v>70037</v>
       </c>
@@ -2854,7 +2872,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A98" s="4">
         <v>70038</v>
       </c>
@@ -2874,7 +2892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A99" s="4">
         <v>70039</v>
       </c>
@@ -2894,7 +2912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A100" s="4">
         <v>70040</v>
       </c>
@@ -2907,8 +2925,14 @@
       <c r="F100" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="J100" s="3">
+        <v>1</v>
+      </c>
+      <c r="K100" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101" s="4">
         <v>70041</v>
       </c>
@@ -2922,7 +2946,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A102" s="4">
         <v>70042</v>
       </c>
@@ -2936,7 +2960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A103" s="4">
         <v>70043</v>
       </c>
@@ -2956,7 +2980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A104" s="4">
         <v>70044</v>
       </c>
@@ -2970,7 +2994,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A105" s="4">
         <v>70045</v>
       </c>
@@ -2990,7 +3014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A106" s="4">
         <v>70046</v>
       </c>
@@ -3007,7 +3031,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A107" s="4">
         <v>70047</v>
       </c>
@@ -3020,8 +3044,14 @@
       <c r="F107" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="J107" s="3">
+        <v>6</v>
+      </c>
+      <c r="K107" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A108" s="4">
         <v>70048</v>
       </c>
@@ -3038,7 +3068,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A109" s="4">
         <v>70049</v>
       </c>
@@ -3057,6 +3087,9 @@
       <c r="I109" s="11"/>
       <c r="L109" s="3">
         <v>3</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DFDFE0-1D20-4AA8-97FF-B04B4EBA15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7A7390-00E0-48BB-8126-C7F0016B4061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_map_editor_config_id_v8" sheetId="1" r:id="rId1"/>
@@ -385,13 +385,13 @@
     <t>6,5,-1,14,1,3000,24,5,-1,36,2,5000,50,5,-1,66,3,7000,84,6,-1,104,6,-1,126,6,-1,150,6,-1,176,6,-1,204,6,-1,234,6,-1,264,6,-1,296,6,-1,330,6,-1</t>
   </si>
   <si>
-    <t>6,30,1800,14,60,1800,24,90,1750,36,120,1750,50,150,1700,66,180,1700,84,210,1650,104,240,1650,126,270,1600,150,300,1600,176,330,1550,204,360,1550,234,390,1500,264,420,1500,296,450,1450,330,500,10000</t>
-  </si>
-  <si>
     <t>6,5,-1,14,1,3000,24,5,-1,36,6,-1,50,5,-1,66,2,4500,84,5,-1,104,5,-1,126,6,-1,150,3,6500,176,5,-1,204,6,-1,234,3,8500,270,5,-1,310,6,-1</t>
   </si>
   <si>
     <t>5,5,-1,12,6,-1,18,6,-1</t>
+  </si>
+  <si>
+    <t>9,40,1400,22,80,1500,39,120,1600,60,160,1700,85,200,1800,112,240,1900,142,280,2000,175,320,2100,211,360,2200,249,400,2300,289,440,2400,330,500,10000</t>
   </si>
 </sst>
 </file>
@@ -492,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -522,6 +522,9 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1152,8 +1155,8 @@
       <c r="G7" s="8">
         <v>2</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>106</v>
+      <c r="I7" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
@@ -1242,8 +1245,8 @@
       <c r="G11" s="8">
         <v>2</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>106</v>
+      <c r="I11" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
@@ -1369,8 +1372,8 @@
       <c r="G17" s="3">
         <v>3</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>106</v>
+      <c r="I17" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
@@ -1472,8 +1475,8 @@
       <c r="G22" s="3">
         <v>3</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>106</v>
+      <c r="I22" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
@@ -1642,8 +1645,8 @@
       <c r="G31" s="3">
         <v>3</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>106</v>
+      <c r="I31" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
@@ -1854,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.15">
@@ -2480,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.15">
@@ -3089,7 +3092,7 @@
         <v>3</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_map_editor_config_id_v8【迷宫-地编配置id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7A7390-00E0-48BB-8126-C7F0016B4061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C48B866-DC2E-45D3-8CFC-26C17B24A0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
     <t>5,5,-1,12,6,-1,18,6,-1</t>
   </si>
   <si>
-    <t>9,40,1400,22,80,1500,39,120,1600,60,160,1700,85,200,1800,112,240,1900,142,280,2000,175,320,2100,211,360,2200,249,400,2300,289,440,2400,330,500,10000</t>
+    <t>9,5,-1,22,5,-1,39,1,3000,60,6,-1,85,5,-1,112,5,-1,142,2,4500,175,6,-1,211,5,-1,249,5,-1,289,6,-1,330,5,-1</t>
   </si>
 </sst>
 </file>
@@ -1109,9 +1109,7 @@
       <c r="G5" s="8">
         <v>1</v>
       </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
@@ -1128,14 +1126,12 @@
         <v>22</v>
       </c>
       <c r="G6" s="8"/>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3">
-        <v>6000</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
@@ -1155,7 +1151,11 @@
       <c r="G7" s="8">
         <v>2</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="12"/>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1178,9 +1178,7 @@
       <c r="G8" s="8">
         <v>1</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
@@ -1201,9 +1199,7 @@
       <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
@@ -1219,14 +1215,12 @@
         <v>28</v>
       </c>
       <c r="G10" s="8"/>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10" s="3">
-        <v>6000</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
@@ -1245,7 +1239,11 @@
       <c r="G11" s="8">
         <v>2</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="12"/>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1269,9 +1267,7 @@
       <c r="G12" s="8">
         <v>1</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
+      <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
@@ -1287,9 +1283,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="8"/>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
@@ -1304,9 +1298,7 @@
       <c r="F14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
@@ -1327,9 +1319,7 @@
       <c r="G15" s="3">
         <v>1</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
@@ -1345,17 +1335,15 @@
       <c r="F16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
+      <c r="I16" s="3"/>
       <c r="J16" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K16" s="3">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>30003</v>
       </c>
@@ -1372,11 +1360,15 @@
       <c r="G17" s="3">
         <v>3</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="12"/>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>30004</v>
       </c>
@@ -1395,11 +1387,9 @@
       <c r="G18" s="3">
         <v>1</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>30005</v>
       </c>
@@ -1413,11 +1403,9 @@
       <c r="F19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>40001</v>
       </c>
@@ -1438,7 +1426,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>40002</v>
       </c>
@@ -1453,13 +1441,13 @@
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K21" s="3">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>40003</v>
       </c>
@@ -1475,11 +1463,15 @@
       <c r="G22" s="3">
         <v>3</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="12"/>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>40004</v>
       </c>
@@ -1500,7 +1492,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>40005</v>
       </c>
@@ -1515,7 +1507,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>40006</v>
       </c>
@@ -1536,7 +1528,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>40007</v>
       </c>
@@ -1554,7 +1546,7 @@
       </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>40008</v>
       </c>
@@ -1569,7 +1561,7 @@
       </c>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>50001</v>
       </c>
@@ -1589,7 +1581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
         <v>50002</v>
       </c>
@@ -1603,13 +1595,13 @@
         <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K29" s="3">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
         <v>50003</v>
       </c>
@@ -1622,14 +1614,8 @@
       <c r="F30" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="3">
-        <v>3</v>
-      </c>
-      <c r="K30" s="3">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>50004</v>
       </c>
@@ -1645,11 +1631,15 @@
       <c r="G31" s="3">
         <v>3</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="12"/>
+      <c r="L31" s="3">
+        <v>1</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>50005</v>
       </c>
